--- a/output/version3/test/20-10/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1149</v>
+        <v>893</v>
       </c>
       <c r="C2" t="n">
-        <v>1048</v>
+        <v>955</v>
       </c>
       <c r="D2" t="n">
-        <v>1026</v>
+        <v>1154</v>
       </c>
       <c r="E2" t="n">
-        <v>1005</v>
+        <v>1126</v>
       </c>
       <c r="F2" t="n">
-        <v>1120</v>
+        <v>1043</v>
       </c>
       <c r="G2" t="n">
-        <v>840</v>
+        <v>982</v>
       </c>
       <c r="H2" t="n">
-        <v>1108</v>
+        <v>920</v>
       </c>
       <c r="I2" t="n">
-        <v>983</v>
+        <v>1089</v>
       </c>
       <c r="J2" t="n">
-        <v>1128</v>
+        <v>922</v>
       </c>
       <c r="K2" t="n">
-        <v>1024</v>
+        <v>1092</v>
       </c>
       <c r="L2" t="n">
-        <v>1043.1</v>
+        <v>1017.6</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>903</v>
+        <v>955</v>
       </c>
       <c r="C3" t="n">
-        <v>888</v>
+        <v>1128</v>
       </c>
       <c r="D3" t="n">
-        <v>1170</v>
+        <v>874</v>
       </c>
       <c r="E3" t="n">
-        <v>1087</v>
+        <v>1022</v>
       </c>
       <c r="F3" t="n">
-        <v>1021</v>
+        <v>857</v>
       </c>
       <c r="G3" t="n">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="H3" t="n">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="I3" t="n">
-        <v>1089</v>
+        <v>833</v>
       </c>
       <c r="J3" t="n">
-        <v>1148</v>
+        <v>1061</v>
       </c>
       <c r="K3" t="n">
-        <v>1158</v>
+        <v>1005</v>
       </c>
       <c r="L3" t="n">
-        <v>1040.4</v>
+        <v>969.1</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>928</v>
+        <v>816</v>
       </c>
       <c r="C4" t="n">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D4" t="n">
-        <v>1027</v>
+        <v>1119</v>
       </c>
       <c r="E4" t="n">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F4" t="n">
-        <v>926</v>
+        <v>1065</v>
       </c>
       <c r="G4" t="n">
-        <v>991</v>
+        <v>886</v>
       </c>
       <c r="H4" t="n">
-        <v>1056</v>
+        <v>892</v>
       </c>
       <c r="I4" t="n">
-        <v>1135</v>
+        <v>943</v>
       </c>
       <c r="J4" t="n">
-        <v>799</v>
+        <v>966</v>
       </c>
       <c r="K4" t="n">
-        <v>1012</v>
+        <v>914</v>
       </c>
       <c r="L4" t="n">
-        <v>996.7</v>
+        <v>954.1</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>932</v>
+        <v>865</v>
       </c>
       <c r="C5" t="n">
-        <v>791</v>
+        <v>871</v>
       </c>
       <c r="D5" t="n">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="E5" t="n">
-        <v>995</v>
+        <v>765</v>
       </c>
       <c r="F5" t="n">
-        <v>1046</v>
+        <v>937</v>
       </c>
       <c r="G5" t="n">
-        <v>901</v>
+        <v>832</v>
       </c>
       <c r="H5" t="n">
-        <v>924</v>
+        <v>866</v>
       </c>
       <c r="I5" t="n">
-        <v>926</v>
+        <v>905</v>
       </c>
       <c r="J5" t="n">
-        <v>871</v>
+        <v>1016</v>
       </c>
       <c r="K5" t="n">
-        <v>852</v>
+        <v>944</v>
       </c>
       <c r="L5" t="n">
-        <v>924.3</v>
+        <v>901.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>961</v>
+        <v>926</v>
       </c>
       <c r="C6" t="n">
-        <v>1006</v>
+        <v>942</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>929</v>
       </c>
       <c r="E6" t="n">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="F6" t="n">
-        <v>1025</v>
+        <v>801</v>
       </c>
       <c r="G6" t="n">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="H6" t="n">
-        <v>958</v>
+        <v>873</v>
       </c>
       <c r="I6" t="n">
-        <v>938</v>
+        <v>837</v>
       </c>
       <c r="J6" t="n">
-        <v>964</v>
+        <v>843</v>
       </c>
       <c r="K6" t="n">
-        <v>1116</v>
+        <v>901</v>
       </c>
       <c r="L6" t="n">
-        <v>968.1</v>
+        <v>885.3</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1043</v>
+        <v>768</v>
       </c>
       <c r="C7" t="n">
-        <v>950</v>
+        <v>773</v>
       </c>
       <c r="D7" t="n">
-        <v>951</v>
+        <v>888</v>
       </c>
       <c r="E7" t="n">
-        <v>836</v>
+        <v>921</v>
       </c>
       <c r="F7" t="n">
-        <v>941</v>
+        <v>774</v>
       </c>
       <c r="G7" t="n">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="H7" t="n">
-        <v>976</v>
+        <v>875</v>
       </c>
       <c r="I7" t="n">
-        <v>972</v>
+        <v>919</v>
       </c>
       <c r="J7" t="n">
-        <v>959</v>
+        <v>838</v>
       </c>
       <c r="K7" t="n">
-        <v>978</v>
+        <v>822</v>
       </c>
       <c r="L7" t="n">
-        <v>952.3</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1040</v>
+        <v>1018</v>
       </c>
       <c r="C8" t="n">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="D8" t="n">
-        <v>908</v>
+        <v>886</v>
       </c>
       <c r="E8" t="n">
-        <v>1012</v>
+        <v>945</v>
       </c>
       <c r="F8" t="n">
-        <v>1047</v>
+        <v>933</v>
       </c>
       <c r="G8" t="n">
-        <v>1057</v>
+        <v>852</v>
       </c>
       <c r="H8" t="n">
-        <v>1281</v>
+        <v>914</v>
       </c>
       <c r="I8" t="n">
-        <v>1098</v>
+        <v>1022</v>
       </c>
       <c r="J8" t="n">
-        <v>1034</v>
+        <v>930</v>
       </c>
       <c r="K8" t="n">
-        <v>1142</v>
+        <v>961</v>
       </c>
       <c r="L8" t="n">
-        <v>1054.6</v>
+        <v>939.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1063</v>
+        <v>919</v>
       </c>
       <c r="C9" t="n">
-        <v>920</v>
+        <v>865</v>
       </c>
       <c r="D9" t="n">
-        <v>966</v>
+        <v>921</v>
       </c>
       <c r="E9" t="n">
-        <v>975</v>
+        <v>890</v>
       </c>
       <c r="F9" t="n">
-        <v>929</v>
+        <v>974</v>
       </c>
       <c r="G9" t="n">
-        <v>1061</v>
+        <v>1001</v>
       </c>
       <c r="H9" t="n">
-        <v>1050</v>
+        <v>1021</v>
       </c>
       <c r="I9" t="n">
-        <v>1154</v>
+        <v>968</v>
       </c>
       <c r="J9" t="n">
-        <v>1015</v>
+        <v>949</v>
       </c>
       <c r="K9" t="n">
-        <v>1181</v>
+        <v>922</v>
       </c>
       <c r="L9" t="n">
-        <v>1031.4</v>
+        <v>943</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="C10" t="n">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D10" t="n">
-        <v>961</v>
+        <v>784</v>
       </c>
       <c r="E10" t="n">
-        <v>827</v>
+        <v>942</v>
       </c>
       <c r="F10" t="n">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="G10" t="n">
-        <v>883</v>
+        <v>824</v>
       </c>
       <c r="H10" t="n">
-        <v>832</v>
+        <v>874</v>
       </c>
       <c r="I10" t="n">
-        <v>1008</v>
+        <v>769</v>
       </c>
       <c r="J10" t="n">
-        <v>895</v>
+        <v>877</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>865</v>
       </c>
       <c r="L10" t="n">
-        <v>896.1</v>
+        <v>858.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="C11" t="n">
-        <v>892</v>
+        <v>833</v>
       </c>
       <c r="D11" t="n">
-        <v>896</v>
+        <v>756</v>
       </c>
       <c r="E11" t="n">
-        <v>912</v>
+        <v>805</v>
       </c>
       <c r="F11" t="n">
-        <v>1019</v>
+        <v>813</v>
       </c>
       <c r="G11" t="n">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="H11" t="n">
-        <v>900</v>
+        <v>849</v>
       </c>
       <c r="I11" t="n">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="J11" t="n">
-        <v>1009</v>
+        <v>1088</v>
       </c>
       <c r="K11" t="n">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="L11" t="n">
-        <v>925.5</v>
+        <v>872.8</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>935</v>
+        <v>981</v>
       </c>
       <c r="C12" t="n">
-        <v>876</v>
+        <v>988</v>
       </c>
       <c r="D12" t="n">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="E12" t="n">
-        <v>988</v>
+        <v>887</v>
       </c>
       <c r="F12" t="n">
-        <v>988</v>
+        <v>898</v>
       </c>
       <c r="G12" t="n">
-        <v>927</v>
+        <v>880</v>
       </c>
       <c r="H12" t="n">
-        <v>1148</v>
+        <v>855</v>
       </c>
       <c r="I12" t="n">
-        <v>944</v>
+        <v>926</v>
       </c>
       <c r="J12" t="n">
-        <v>1062</v>
+        <v>980</v>
       </c>
       <c r="K12" t="n">
-        <v>1093</v>
+        <v>954</v>
       </c>
       <c r="L12" t="n">
-        <v>988.3</v>
+        <v>925.1</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>982</v>
+        <v>1088</v>
       </c>
       <c r="C13" t="n">
-        <v>827</v>
+        <v>899</v>
       </c>
       <c r="D13" t="n">
-        <v>922</v>
+        <v>865</v>
       </c>
       <c r="E13" t="n">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="F13" t="n">
-        <v>867</v>
+        <v>813</v>
       </c>
       <c r="G13" t="n">
-        <v>920</v>
+        <v>837</v>
       </c>
       <c r="H13" t="n">
-        <v>1020</v>
+        <v>835</v>
       </c>
       <c r="I13" t="n">
-        <v>1029</v>
+        <v>805</v>
       </c>
       <c r="J13" t="n">
-        <v>931</v>
+        <v>898</v>
       </c>
       <c r="K13" t="n">
-        <v>1113</v>
+        <v>959</v>
       </c>
       <c r="L13" t="n">
-        <v>952</v>
+        <v>892.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1065</v>
+        <v>848</v>
       </c>
       <c r="C14" t="n">
-        <v>898</v>
+        <v>851</v>
       </c>
       <c r="D14" t="n">
-        <v>982</v>
+        <v>854</v>
       </c>
       <c r="E14" t="n">
-        <v>936</v>
+        <v>955</v>
       </c>
       <c r="F14" t="n">
-        <v>928</v>
+        <v>1162</v>
       </c>
       <c r="G14" t="n">
-        <v>940</v>
+        <v>995</v>
       </c>
       <c r="H14" t="n">
-        <v>1187</v>
+        <v>950</v>
       </c>
       <c r="I14" t="n">
-        <v>939</v>
+        <v>816</v>
       </c>
       <c r="J14" t="n">
-        <v>984</v>
+        <v>803</v>
       </c>
       <c r="K14" t="n">
-        <v>1201</v>
+        <v>860</v>
       </c>
       <c r="L14" t="n">
-        <v>1006</v>
+        <v>909.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1181</v>
+        <v>969</v>
       </c>
       <c r="C15" t="n">
-        <v>966</v>
+        <v>1063</v>
       </c>
       <c r="D15" t="n">
-        <v>1086</v>
+        <v>1050</v>
       </c>
       <c r="E15" t="n">
-        <v>1162</v>
+        <v>924</v>
       </c>
       <c r="F15" t="n">
-        <v>1096</v>
+        <v>1040</v>
       </c>
       <c r="G15" t="n">
-        <v>1044</v>
+        <v>981</v>
       </c>
       <c r="H15" t="n">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="I15" t="n">
-        <v>955</v>
+        <v>1027</v>
       </c>
       <c r="J15" t="n">
-        <v>1104</v>
+        <v>920</v>
       </c>
       <c r="K15" t="n">
-        <v>1077</v>
+        <v>920</v>
       </c>
       <c r="L15" t="n">
-        <v>1064</v>
+        <v>985.3</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>987</v>
+        <v>865</v>
       </c>
       <c r="C16" t="n">
-        <v>1057</v>
+        <v>1127</v>
       </c>
       <c r="D16" t="n">
-        <v>1144</v>
+        <v>992</v>
       </c>
       <c r="E16" t="n">
-        <v>1130</v>
+        <v>935</v>
       </c>
       <c r="F16" t="n">
-        <v>969</v>
+        <v>904</v>
       </c>
       <c r="G16" t="n">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="H16" t="n">
-        <v>977</v>
+        <v>830</v>
       </c>
       <c r="I16" t="n">
-        <v>1071</v>
+        <v>979</v>
       </c>
       <c r="J16" t="n">
-        <v>961</v>
+        <v>891</v>
       </c>
       <c r="K16" t="n">
-        <v>947</v>
+        <v>1164</v>
       </c>
       <c r="L16" t="n">
-        <v>1017.4</v>
+        <v>960.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>888</v>
+        <v>791</v>
       </c>
       <c r="C17" t="n">
-        <v>847</v>
+        <v>930</v>
       </c>
       <c r="D17" t="n">
-        <v>907</v>
+        <v>779</v>
       </c>
       <c r="E17" t="n">
-        <v>987</v>
+        <v>825</v>
       </c>
       <c r="F17" t="n">
-        <v>951</v>
+        <v>895</v>
       </c>
       <c r="G17" t="n">
-        <v>995</v>
+        <v>853</v>
       </c>
       <c r="H17" t="n">
-        <v>946</v>
+        <v>788</v>
       </c>
       <c r="I17" t="n">
-        <v>989</v>
+        <v>834</v>
       </c>
       <c r="J17" t="n">
-        <v>1024</v>
+        <v>910</v>
       </c>
       <c r="K17" t="n">
-        <v>1081</v>
+        <v>824</v>
       </c>
       <c r="L17" t="n">
-        <v>961.5</v>
+        <v>842.9</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>989</v>
+        <v>917</v>
       </c>
       <c r="C18" t="n">
-        <v>899</v>
+        <v>1011</v>
       </c>
       <c r="D18" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E18" t="n">
         <v>1015</v>
       </c>
-      <c r="E18" t="n">
-        <v>963</v>
-      </c>
       <c r="F18" t="n">
-        <v>947</v>
+        <v>991</v>
       </c>
       <c r="G18" t="n">
-        <v>1208</v>
+        <v>1030</v>
       </c>
       <c r="H18" t="n">
-        <v>988</v>
+        <v>938</v>
       </c>
       <c r="I18" t="n">
-        <v>846</v>
+        <v>1012</v>
       </c>
       <c r="J18" t="n">
-        <v>1007</v>
+        <v>800</v>
       </c>
       <c r="K18" t="n">
-        <v>891</v>
+        <v>1013</v>
       </c>
       <c r="L18" t="n">
-        <v>975.3</v>
+        <v>980.2</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>880</v>
+        <v>787</v>
       </c>
       <c r="C19" t="n">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="D19" t="n">
-        <v>1111</v>
+        <v>904</v>
       </c>
       <c r="E19" t="n">
-        <v>914</v>
+        <v>754</v>
       </c>
       <c r="F19" t="n">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G19" t="n">
-        <v>903</v>
+        <v>786</v>
       </c>
       <c r="H19" t="n">
-        <v>975</v>
+        <v>788</v>
       </c>
       <c r="I19" t="n">
-        <v>851</v>
+        <v>867</v>
       </c>
       <c r="J19" t="n">
-        <v>919</v>
+        <v>765</v>
       </c>
       <c r="K19" t="n">
-        <v>889</v>
+        <v>751</v>
       </c>
       <c r="L19" t="n">
-        <v>920.3</v>
+        <v>817.7</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>872</v>
+        <v>902</v>
       </c>
       <c r="C20" t="n">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="D20" t="n">
-        <v>874</v>
+        <v>732</v>
       </c>
       <c r="E20" t="n">
-        <v>1068</v>
+        <v>878</v>
       </c>
       <c r="F20" t="n">
-        <v>847</v>
+        <v>883</v>
       </c>
       <c r="G20" t="n">
-        <v>1023</v>
+        <v>948</v>
       </c>
       <c r="H20" t="n">
-        <v>1126</v>
+        <v>959</v>
       </c>
       <c r="I20" t="n">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="J20" t="n">
-        <v>971</v>
+        <v>827</v>
       </c>
       <c r="K20" t="n">
-        <v>1012</v>
+        <v>911</v>
       </c>
       <c r="L20" t="n">
-        <v>954.4</v>
+        <v>876.4</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1061</v>
+        <v>998</v>
       </c>
       <c r="C21" t="n">
-        <v>890</v>
+        <v>988</v>
       </c>
       <c r="D21" t="n">
-        <v>1111</v>
+        <v>968</v>
       </c>
       <c r="E21" t="n">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="F21" t="n">
-        <v>1133</v>
+        <v>954</v>
       </c>
       <c r="G21" t="n">
-        <v>1190</v>
+        <v>946</v>
       </c>
       <c r="H21" t="n">
-        <v>1334</v>
+        <v>882</v>
       </c>
       <c r="I21" t="n">
-        <v>1200</v>
+        <v>817</v>
       </c>
       <c r="J21" t="n">
-        <v>1059</v>
+        <v>797</v>
       </c>
       <c r="K21" t="n">
-        <v>1047</v>
+        <v>926</v>
       </c>
       <c r="L21" t="n">
-        <v>1099.6</v>
+        <v>924.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1062</v>
+        <v>811</v>
       </c>
       <c r="C22" t="n">
-        <v>943</v>
+        <v>853</v>
       </c>
       <c r="D22" t="n">
-        <v>925</v>
+        <v>856</v>
       </c>
       <c r="E22" t="n">
-        <v>923</v>
+        <v>821</v>
       </c>
       <c r="F22" t="n">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="G22" t="n">
-        <v>941</v>
+        <v>778</v>
       </c>
       <c r="H22" t="n">
-        <v>997</v>
+        <v>847</v>
       </c>
       <c r="I22" t="n">
-        <v>1016</v>
+        <v>779</v>
       </c>
       <c r="J22" t="n">
-        <v>888</v>
+        <v>966</v>
       </c>
       <c r="K22" t="n">
-        <v>1101</v>
+        <v>822</v>
       </c>
       <c r="L22" t="n">
-        <v>970.9</v>
+        <v>846</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1059</v>
+        <v>1023</v>
       </c>
       <c r="C23" t="n">
-        <v>1048</v>
+        <v>969</v>
       </c>
       <c r="D23" t="n">
-        <v>1056</v>
+        <v>1011</v>
       </c>
       <c r="E23" t="n">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="F23" t="n">
-        <v>1092</v>
+        <v>881</v>
       </c>
       <c r="G23" t="n">
-        <v>1071</v>
+        <v>922</v>
       </c>
       <c r="H23" t="n">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="I23" t="n">
-        <v>1180</v>
+        <v>855</v>
       </c>
       <c r="J23" t="n">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="K23" t="n">
-        <v>1132</v>
+        <v>891</v>
       </c>
       <c r="L23" t="n">
-        <v>1072.5</v>
+        <v>963</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>926</v>
+        <v>989</v>
       </c>
       <c r="C24" t="n">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="D24" t="n">
-        <v>914</v>
+        <v>927</v>
       </c>
       <c r="E24" t="n">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="F24" t="n">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="G24" t="n">
-        <v>941</v>
+        <v>834</v>
       </c>
       <c r="H24" t="n">
-        <v>894</v>
+        <v>858</v>
       </c>
       <c r="I24" t="n">
-        <v>1013</v>
+        <v>849</v>
       </c>
       <c r="J24" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="K24" t="n">
-        <v>994</v>
+        <v>964</v>
       </c>
       <c r="L24" t="n">
-        <v>901.6</v>
+        <v>880.3</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1079</v>
+        <v>901</v>
       </c>
       <c r="C25" t="n">
-        <v>994</v>
+        <v>930</v>
       </c>
       <c r="D25" t="n">
-        <v>1119</v>
+        <v>937</v>
       </c>
       <c r="E25" t="n">
-        <v>1194</v>
+        <v>1122</v>
       </c>
       <c r="F25" t="n">
-        <v>1124</v>
+        <v>898</v>
       </c>
       <c r="G25" t="n">
-        <v>1055</v>
+        <v>950</v>
       </c>
       <c r="H25" t="n">
-        <v>1062</v>
+        <v>969</v>
       </c>
       <c r="I25" t="n">
-        <v>972</v>
+        <v>1028</v>
       </c>
       <c r="J25" t="n">
-        <v>926</v>
+        <v>963</v>
       </c>
       <c r="K25" t="n">
-        <v>936</v>
+        <v>907</v>
       </c>
       <c r="L25" t="n">
-        <v>1046.1</v>
+        <v>960.5</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1106</v>
+        <v>969</v>
       </c>
       <c r="C26" t="n">
-        <v>1077</v>
+        <v>954</v>
       </c>
       <c r="D26" t="n">
-        <v>1090</v>
+        <v>1007</v>
       </c>
       <c r="E26" t="n">
-        <v>1044</v>
+        <v>998</v>
       </c>
       <c r="F26" t="n">
-        <v>1103</v>
+        <v>924</v>
       </c>
       <c r="G26" t="n">
-        <v>1166</v>
+        <v>943</v>
       </c>
       <c r="H26" t="n">
-        <v>1216</v>
+        <v>941</v>
       </c>
       <c r="I26" t="n">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="J26" t="n">
-        <v>1087</v>
+        <v>1149</v>
       </c>
       <c r="K26" t="n">
-        <v>1275</v>
+        <v>937</v>
       </c>
       <c r="L26" t="n">
-        <v>1106.8</v>
+        <v>972.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1155</v>
+        <v>942</v>
       </c>
       <c r="C27" t="n">
-        <v>1116</v>
+        <v>1051</v>
       </c>
       <c r="D27" t="n">
-        <v>1148</v>
+        <v>948</v>
       </c>
       <c r="E27" t="n">
-        <v>1059</v>
+        <v>995</v>
       </c>
       <c r="F27" t="n">
-        <v>1089</v>
+        <v>1004</v>
       </c>
       <c r="G27" t="n">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="H27" t="n">
-        <v>1135</v>
+        <v>895</v>
       </c>
       <c r="I27" t="n">
-        <v>1206</v>
+        <v>1156</v>
       </c>
       <c r="J27" t="n">
-        <v>1129</v>
+        <v>896</v>
       </c>
       <c r="K27" t="n">
-        <v>1141</v>
+        <v>941</v>
       </c>
       <c r="L27" t="n">
-        <v>1124.4</v>
+        <v>990</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>940</v>
+        <v>908</v>
       </c>
       <c r="C28" t="n">
-        <v>872</v>
+        <v>891</v>
       </c>
       <c r="D28" t="n">
-        <v>905</v>
+        <v>865</v>
       </c>
       <c r="E28" t="n">
-        <v>1007</v>
+        <v>818</v>
       </c>
       <c r="F28" t="n">
-        <v>918</v>
+        <v>806</v>
       </c>
       <c r="G28" t="n">
-        <v>961</v>
+        <v>753</v>
       </c>
       <c r="H28" t="n">
-        <v>948</v>
+        <v>894</v>
       </c>
       <c r="I28" t="n">
-        <v>1002</v>
+        <v>873</v>
       </c>
       <c r="J28" t="n">
-        <v>1099</v>
+        <v>779</v>
       </c>
       <c r="K28" t="n">
-        <v>1061</v>
+        <v>914</v>
       </c>
       <c r="L28" t="n">
-        <v>971.3</v>
+        <v>850.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1088</v>
+        <v>890</v>
       </c>
       <c r="C29" t="n">
-        <v>936</v>
+        <v>1011</v>
       </c>
       <c r="D29" t="n">
-        <v>936</v>
+        <v>830</v>
       </c>
       <c r="E29" t="n">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="F29" t="n">
-        <v>1028</v>
+        <v>891</v>
       </c>
       <c r="G29" t="n">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="H29" t="n">
-        <v>1122</v>
+        <v>900</v>
       </c>
       <c r="I29" t="n">
-        <v>987</v>
+        <v>800</v>
       </c>
       <c r="J29" t="n">
-        <v>1074</v>
+        <v>873</v>
       </c>
       <c r="K29" t="n">
-        <v>1075</v>
+        <v>815</v>
       </c>
       <c r="L29" t="n">
-        <v>997.3</v>
+        <v>875.6</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>784</v>
+        <v>953</v>
       </c>
       <c r="C30" t="n">
-        <v>948</v>
+        <v>884</v>
       </c>
       <c r="D30" t="n">
-        <v>945</v>
+        <v>817</v>
       </c>
       <c r="E30" t="n">
-        <v>896</v>
+        <v>865</v>
       </c>
       <c r="F30" t="n">
-        <v>974</v>
+        <v>893</v>
       </c>
       <c r="G30" t="n">
-        <v>946</v>
+        <v>889</v>
       </c>
       <c r="H30" t="n">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="I30" t="n">
-        <v>898</v>
+        <v>831</v>
       </c>
       <c r="J30" t="n">
-        <v>949</v>
+        <v>876</v>
       </c>
       <c r="K30" t="n">
-        <v>1022</v>
+        <v>843</v>
       </c>
       <c r="L30" t="n">
-        <v>935.9</v>
+        <v>883.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>932</v>
+        <v>1027</v>
       </c>
       <c r="C31" t="n">
-        <v>1016</v>
+        <v>875</v>
       </c>
       <c r="D31" t="n">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="E31" t="n">
-        <v>1168</v>
+        <v>915</v>
       </c>
       <c r="F31" t="n">
-        <v>904</v>
+        <v>1093</v>
       </c>
       <c r="G31" t="n">
-        <v>1082</v>
+        <v>835</v>
       </c>
       <c r="H31" t="n">
-        <v>968</v>
+        <v>933</v>
       </c>
       <c r="I31" t="n">
-        <v>879</v>
+        <v>1035</v>
       </c>
       <c r="J31" t="n">
-        <v>889</v>
+        <v>822</v>
       </c>
       <c r="K31" t="n">
-        <v>927</v>
+        <v>1047</v>
       </c>
       <c r="L31" t="n">
-        <v>970.7</v>
+        <v>953.3</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1084</v>
+        <v>1052</v>
       </c>
       <c r="C32" t="n">
-        <v>1099</v>
+        <v>1116</v>
       </c>
       <c r="D32" t="n">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="E32" t="n">
-        <v>1277</v>
+        <v>1188</v>
       </c>
       <c r="F32" t="n">
-        <v>1095</v>
+        <v>879</v>
       </c>
       <c r="G32" t="n">
         <v>1151</v>
       </c>
       <c r="H32" t="n">
-        <v>1192</v>
+        <v>1166</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>1127</v>
       </c>
       <c r="J32" t="n">
-        <v>1052</v>
+        <v>1128</v>
       </c>
       <c r="K32" t="n">
-        <v>1024</v>
+        <v>1081</v>
       </c>
       <c r="L32" t="n">
-        <v>1105.7</v>
+        <v>1098.3</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>961</v>
+        <v>897</v>
       </c>
       <c r="C33" t="n">
-        <v>1030</v>
+        <v>866</v>
       </c>
       <c r="D33" t="n">
+        <v>928</v>
+      </c>
+      <c r="E33" t="n">
         <v>889</v>
       </c>
-      <c r="E33" t="n">
-        <v>973</v>
-      </c>
       <c r="F33" t="n">
-        <v>975</v>
+        <v>905</v>
       </c>
       <c r="G33" t="n">
-        <v>1098</v>
+        <v>865</v>
       </c>
       <c r="H33" t="n">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="I33" t="n">
-        <v>1035</v>
+        <v>890</v>
       </c>
       <c r="J33" t="n">
-        <v>876</v>
+        <v>808</v>
       </c>
       <c r="K33" t="n">
-        <v>930</v>
+        <v>963</v>
       </c>
       <c r="L33" t="n">
-        <v>977.4</v>
+        <v>905.4</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>987</v>
+        <v>972</v>
       </c>
       <c r="C34" t="n">
-        <v>1162</v>
+        <v>928</v>
       </c>
       <c r="D34" t="n">
-        <v>1048</v>
+        <v>974</v>
       </c>
       <c r="E34" t="n">
-        <v>1113</v>
+        <v>968</v>
       </c>
       <c r="F34" t="n">
-        <v>1040</v>
+        <v>951</v>
       </c>
       <c r="G34" t="n">
-        <v>967</v>
+        <v>920</v>
       </c>
       <c r="H34" t="n">
-        <v>1053</v>
+        <v>985</v>
       </c>
       <c r="I34" t="n">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="J34" t="n">
-        <v>824</v>
+        <v>960</v>
       </c>
       <c r="K34" t="n">
-        <v>1068</v>
+        <v>948</v>
       </c>
       <c r="L34" t="n">
-        <v>1024.4</v>
+        <v>958.6</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1020</v>
+        <v>919</v>
       </c>
       <c r="C35" t="n">
-        <v>1000</v>
+        <v>1065</v>
       </c>
       <c r="D35" t="n">
-        <v>1058</v>
+        <v>906</v>
       </c>
       <c r="E35" t="n">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F35" t="n">
-        <v>1033</v>
+        <v>903</v>
       </c>
       <c r="G35" t="n">
-        <v>1074</v>
+        <v>981</v>
       </c>
       <c r="H35" t="n">
-        <v>1045</v>
+        <v>903</v>
       </c>
       <c r="I35" t="n">
-        <v>912</v>
+        <v>934</v>
       </c>
       <c r="J35" t="n">
-        <v>1011</v>
+        <v>974</v>
       </c>
       <c r="K35" t="n">
-        <v>1139</v>
+        <v>881</v>
       </c>
       <c r="L35" t="n">
-        <v>1027.4</v>
+        <v>945</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1036</v>
+        <v>1078</v>
       </c>
       <c r="C36" t="n">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="D36" t="n">
-        <v>859</v>
+        <v>937</v>
       </c>
       <c r="E36" t="n">
-        <v>1093</v>
+        <v>898</v>
       </c>
       <c r="F36" t="n">
-        <v>1043</v>
+        <v>955</v>
       </c>
       <c r="G36" t="n">
-        <v>893</v>
+        <v>921</v>
       </c>
       <c r="H36" t="n">
-        <v>1089</v>
+        <v>990</v>
       </c>
       <c r="I36" t="n">
-        <v>1090</v>
+        <v>899</v>
       </c>
       <c r="J36" t="n">
-        <v>983</v>
+        <v>1014</v>
       </c>
       <c r="K36" t="n">
-        <v>1090</v>
+        <v>927</v>
       </c>
       <c r="L36" t="n">
-        <v>1011.6</v>
+        <v>958</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1119</v>
+        <v>980</v>
       </c>
       <c r="C37" t="n">
-        <v>966</v>
+        <v>841</v>
       </c>
       <c r="D37" t="n">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="E37" t="n">
-        <v>1074</v>
+        <v>848</v>
       </c>
       <c r="F37" t="n">
-        <v>983</v>
+        <v>786</v>
       </c>
       <c r="G37" t="n">
-        <v>1125</v>
+        <v>798</v>
       </c>
       <c r="H37" t="n">
-        <v>808</v>
+        <v>944</v>
       </c>
       <c r="I37" t="n">
-        <v>1006</v>
+        <v>878</v>
       </c>
       <c r="J37" t="n">
-        <v>938</v>
+        <v>982</v>
       </c>
       <c r="K37" t="n">
-        <v>994</v>
+        <v>881</v>
       </c>
       <c r="L37" t="n">
-        <v>992.4</v>
+        <v>885.1</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1032</v>
+        <v>793</v>
       </c>
       <c r="C38" t="n">
-        <v>945</v>
+        <v>845</v>
       </c>
       <c r="D38" t="n">
-        <v>970</v>
+        <v>805</v>
       </c>
       <c r="E38" t="n">
-        <v>989</v>
+        <v>911</v>
       </c>
       <c r="F38" t="n">
-        <v>831</v>
+        <v>847</v>
       </c>
       <c r="G38" t="n">
-        <v>1089</v>
+        <v>785</v>
       </c>
       <c r="H38" t="n">
-        <v>880</v>
+        <v>783</v>
       </c>
       <c r="I38" t="n">
-        <v>1005</v>
+        <v>841</v>
       </c>
       <c r="J38" t="n">
-        <v>1083</v>
+        <v>908</v>
       </c>
       <c r="K38" t="n">
-        <v>929</v>
+        <v>914</v>
       </c>
       <c r="L38" t="n">
-        <v>975.3</v>
+        <v>843.2</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="C39" t="n">
-        <v>981</v>
+        <v>837</v>
       </c>
       <c r="D39" t="n">
+        <v>906</v>
+      </c>
+      <c r="E39" t="n">
+        <v>857</v>
+      </c>
+      <c r="F39" t="n">
+        <v>926</v>
+      </c>
+      <c r="G39" t="n">
+        <v>870</v>
+      </c>
+      <c r="H39" t="n">
+        <v>909</v>
+      </c>
+      <c r="I39" t="n">
         <v>924</v>
       </c>
-      <c r="E39" t="n">
-        <v>1029</v>
-      </c>
-      <c r="F39" t="n">
-        <v>971</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1061</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1055</v>
-      </c>
-      <c r="I39" t="n">
-        <v>949</v>
-      </c>
       <c r="J39" t="n">
-        <v>903</v>
+        <v>867</v>
       </c>
       <c r="K39" t="n">
-        <v>866</v>
+        <v>890</v>
       </c>
       <c r="L39" t="n">
-        <v>961.8</v>
+        <v>887.6</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>911</v>
+        <v>836</v>
       </c>
       <c r="C40" t="n">
-        <v>870</v>
+        <v>799</v>
       </c>
       <c r="D40" t="n">
-        <v>935</v>
+        <v>1027</v>
       </c>
       <c r="E40" t="n">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="F40" t="n">
-        <v>861</v>
+        <v>954</v>
       </c>
       <c r="G40" t="n">
-        <v>1097</v>
+        <v>906</v>
       </c>
       <c r="H40" t="n">
-        <v>1046</v>
+        <v>889</v>
       </c>
       <c r="I40" t="n">
-        <v>950</v>
+        <v>866</v>
       </c>
       <c r="J40" t="n">
-        <v>857</v>
+        <v>786</v>
       </c>
       <c r="K40" t="n">
-        <v>1022</v>
+        <v>849</v>
       </c>
       <c r="L40" t="n">
-        <v>944.8</v>
+        <v>881.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>956</v>
+        <v>832</v>
       </c>
       <c r="C41" t="n">
-        <v>814</v>
+        <v>827</v>
       </c>
       <c r="D41" t="n">
-        <v>945</v>
+        <v>927</v>
       </c>
       <c r="E41" t="n">
-        <v>1007</v>
+        <v>776</v>
       </c>
       <c r="F41" t="n">
-        <v>1071</v>
+        <v>828</v>
       </c>
       <c r="G41" t="n">
-        <v>892</v>
+        <v>797</v>
       </c>
       <c r="H41" t="n">
-        <v>915</v>
+        <v>826</v>
       </c>
       <c r="I41" t="n">
-        <v>858</v>
+        <v>700</v>
       </c>
       <c r="J41" t="n">
-        <v>810</v>
+        <v>771</v>
       </c>
       <c r="K41" t="n">
-        <v>852</v>
+        <v>913</v>
       </c>
       <c r="L41" t="n">
-        <v>912</v>
+        <v>819.7</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>981</v>
+        <v>761</v>
       </c>
       <c r="C42" t="n">
-        <v>1147</v>
+        <v>768</v>
       </c>
       <c r="D42" t="n">
-        <v>973</v>
+        <v>860</v>
       </c>
       <c r="E42" t="n">
-        <v>947</v>
+        <v>890</v>
       </c>
       <c r="F42" t="n">
-        <v>937</v>
+        <v>796</v>
       </c>
       <c r="G42" t="n">
-        <v>1019</v>
+        <v>825</v>
       </c>
       <c r="H42" t="n">
-        <v>892</v>
+        <v>799</v>
       </c>
       <c r="I42" t="n">
-        <v>950</v>
+        <v>820</v>
       </c>
       <c r="J42" t="n">
-        <v>886</v>
+        <v>832</v>
       </c>
       <c r="K42" t="n">
-        <v>1058</v>
+        <v>832</v>
       </c>
       <c r="L42" t="n">
-        <v>979</v>
+        <v>818.3</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>997</v>
+        <v>860</v>
       </c>
       <c r="C43" t="n">
-        <v>1134</v>
+        <v>885</v>
       </c>
       <c r="D43" t="n">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="E43" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="F43" t="n">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="G43" t="n">
-        <v>887</v>
+        <v>1083</v>
       </c>
       <c r="H43" t="n">
-        <v>974</v>
+        <v>867</v>
       </c>
       <c r="I43" t="n">
-        <v>1099</v>
+        <v>867</v>
       </c>
       <c r="J43" t="n">
-        <v>1054</v>
+        <v>881</v>
       </c>
       <c r="K43" t="n">
-        <v>936</v>
+        <v>795</v>
       </c>
       <c r="L43" t="n">
-        <v>990.2</v>
+        <v>897</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>856</v>
+        <v>727</v>
       </c>
       <c r="C44" t="n">
-        <v>889</v>
+        <v>793</v>
       </c>
       <c r="D44" t="n">
-        <v>885</v>
+        <v>789</v>
       </c>
       <c r="E44" t="n">
+        <v>739</v>
+      </c>
+      <c r="F44" t="n">
+        <v>846</v>
+      </c>
+      <c r="G44" t="n">
+        <v>826</v>
+      </c>
+      <c r="H44" t="n">
         <v>855</v>
       </c>
-      <c r="F44" t="n">
-        <v>997</v>
-      </c>
-      <c r="G44" t="n">
-        <v>924</v>
-      </c>
-      <c r="H44" t="n">
-        <v>832</v>
-      </c>
       <c r="I44" t="n">
-        <v>807</v>
+        <v>769</v>
       </c>
       <c r="J44" t="n">
-        <v>959</v>
+        <v>783</v>
       </c>
       <c r="K44" t="n">
-        <v>1065</v>
+        <v>892</v>
       </c>
       <c r="L44" t="n">
-        <v>906.9</v>
+        <v>801.9</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1002</v>
+        <v>1135</v>
       </c>
       <c r="C45" t="n">
-        <v>1121</v>
+        <v>1058</v>
       </c>
       <c r="D45" t="n">
-        <v>1098</v>
+        <v>1011</v>
       </c>
       <c r="E45" t="n">
-        <v>1181</v>
+        <v>969</v>
       </c>
       <c r="F45" t="n">
-        <v>1072</v>
+        <v>1017</v>
       </c>
       <c r="G45" t="n">
-        <v>1068</v>
+        <v>992</v>
       </c>
       <c r="H45" t="n">
-        <v>1204</v>
+        <v>988</v>
       </c>
       <c r="I45" t="n">
-        <v>1116</v>
+        <v>959</v>
       </c>
       <c r="J45" t="n">
-        <v>965</v>
+        <v>1056</v>
       </c>
       <c r="K45" t="n">
-        <v>1222</v>
+        <v>1075</v>
       </c>
       <c r="L45" t="n">
-        <v>1104.9</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>891</v>
+        <v>855</v>
       </c>
       <c r="C46" t="n">
-        <v>1011</v>
+        <v>1035</v>
       </c>
       <c r="D46" t="n">
-        <v>973</v>
+        <v>834</v>
       </c>
       <c r="E46" t="n">
-        <v>978</v>
+        <v>886</v>
       </c>
       <c r="F46" t="n">
-        <v>1123</v>
+        <v>855</v>
       </c>
       <c r="G46" t="n">
-        <v>1037</v>
+        <v>844</v>
       </c>
       <c r="H46" t="n">
-        <v>1074</v>
+        <v>834</v>
       </c>
       <c r="I46" t="n">
-        <v>895</v>
+        <v>863</v>
       </c>
       <c r="J46" t="n">
-        <v>987</v>
+        <v>835</v>
       </c>
       <c r="K46" t="n">
-        <v>939</v>
+        <v>985</v>
       </c>
       <c r="L46" t="n">
-        <v>990.8</v>
+        <v>882.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1086</v>
+        <v>896</v>
       </c>
       <c r="C47" t="n">
-        <v>1150</v>
+        <v>1015</v>
       </c>
       <c r="D47" t="n">
-        <v>998</v>
+        <v>948</v>
       </c>
       <c r="E47" t="n">
+        <v>951</v>
+      </c>
+      <c r="F47" t="n">
+        <v>902</v>
+      </c>
+      <c r="G47" t="n">
+        <v>927</v>
+      </c>
+      <c r="H47" t="n">
+        <v>969</v>
+      </c>
+      <c r="I47" t="n">
         <v>933</v>
       </c>
-      <c r="F47" t="n">
-        <v>1094</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1195</v>
-      </c>
-      <c r="H47" t="n">
-        <v>948</v>
-      </c>
-      <c r="I47" t="n">
-        <v>955</v>
-      </c>
       <c r="J47" t="n">
-        <v>1008</v>
+        <v>949</v>
       </c>
       <c r="K47" t="n">
-        <v>1061</v>
+        <v>843</v>
       </c>
       <c r="L47" t="n">
-        <v>1042.8</v>
+        <v>933.3</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="C48" t="n">
-        <v>1005</v>
+        <v>842</v>
       </c>
       <c r="D48" t="n">
-        <v>895</v>
+        <v>707</v>
       </c>
       <c r="E48" t="n">
-        <v>808</v>
+        <v>767</v>
       </c>
       <c r="F48" t="n">
-        <v>949</v>
+        <v>875</v>
       </c>
       <c r="G48" t="n">
-        <v>873</v>
+        <v>774</v>
       </c>
       <c r="H48" t="n">
-        <v>942</v>
+        <v>874</v>
       </c>
       <c r="I48" t="n">
-        <v>957</v>
+        <v>793</v>
       </c>
       <c r="J48" t="n">
-        <v>858</v>
+        <v>772</v>
       </c>
       <c r="K48" t="n">
-        <v>983</v>
+        <v>807</v>
       </c>
       <c r="L48" t="n">
-        <v>910.3</v>
+        <v>803.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1085</v>
+        <v>969</v>
       </c>
       <c r="C49" t="n">
-        <v>1025</v>
+        <v>920</v>
       </c>
       <c r="D49" t="n">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="E49" t="n">
-        <v>940</v>
+        <v>868</v>
       </c>
       <c r="F49" t="n">
-        <v>1029</v>
+        <v>947</v>
       </c>
       <c r="G49" t="n">
-        <v>1028</v>
+        <v>851</v>
       </c>
       <c r="H49" t="n">
-        <v>974</v>
+        <v>868</v>
       </c>
       <c r="I49" t="n">
-        <v>896</v>
+        <v>850</v>
       </c>
       <c r="J49" t="n">
-        <v>1077</v>
+        <v>930</v>
       </c>
       <c r="K49" t="n">
-        <v>845</v>
+        <v>943</v>
       </c>
       <c r="L49" t="n">
-        <v>982.2</v>
+        <v>906</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>926</v>
+        <v>916</v>
       </c>
       <c r="C50" t="n">
-        <v>1027</v>
+        <v>859</v>
       </c>
       <c r="D50" t="n">
-        <v>915</v>
+        <v>894</v>
       </c>
       <c r="E50" t="n">
-        <v>998</v>
+        <v>818</v>
       </c>
       <c r="F50" t="n">
-        <v>922</v>
+        <v>882</v>
       </c>
       <c r="G50" t="n">
-        <v>1029</v>
+        <v>882</v>
       </c>
       <c r="H50" t="n">
-        <v>970</v>
+        <v>787</v>
       </c>
       <c r="I50" t="n">
-        <v>1006</v>
+        <v>983</v>
       </c>
       <c r="J50" t="n">
-        <v>922</v>
+        <v>897</v>
       </c>
       <c r="K50" t="n">
-        <v>995</v>
+        <v>784</v>
       </c>
       <c r="L50" t="n">
-        <v>971</v>
+        <v>870.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="C51" t="n">
-        <v>898</v>
+        <v>860</v>
       </c>
       <c r="D51" t="n">
-        <v>1023</v>
+        <v>936</v>
       </c>
       <c r="E51" t="n">
-        <v>793</v>
+        <v>1026</v>
       </c>
       <c r="F51" t="n">
-        <v>1007</v>
+        <v>956</v>
       </c>
       <c r="G51" t="n">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="H51" t="n">
-        <v>1042</v>
+        <v>958</v>
       </c>
       <c r="I51" t="n">
-        <v>952</v>
+        <v>878</v>
       </c>
       <c r="J51" t="n">
-        <v>888</v>
+        <v>874</v>
       </c>
       <c r="K51" t="n">
-        <v>825</v>
+        <v>863</v>
       </c>
       <c r="L51" t="n">
-        <v>918.3</v>
+        <v>908.5</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>984.8200000000001</v>
+        <v>910.16</v>
       </c>
       <c r="C52" t="n">
-        <v>962.16</v>
+        <v>918.9</v>
       </c>
       <c r="D52" t="n">
-        <v>983.28</v>
+        <v>916.72</v>
       </c>
       <c r="E52" t="n">
-        <v>991.26</v>
+        <v>914.74</v>
       </c>
       <c r="F52" t="n">
-        <v>988.6</v>
+        <v>910.7</v>
       </c>
       <c r="G52" t="n">
-        <v>999.5</v>
+        <v>899.24</v>
       </c>
       <c r="H52" t="n">
-        <v>1022.36</v>
+        <v>908.38</v>
       </c>
       <c r="I52" t="n">
-        <v>988.3</v>
+        <v>900.84</v>
       </c>
       <c r="J52" t="n">
-        <v>974.86</v>
+        <v>906.42</v>
       </c>
       <c r="K52" t="n">
-        <v>1024.46</v>
+        <v>915.7</v>
       </c>
       <c r="L52" t="n">
-        <v>991.96</v>
+        <v>910.1799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8.466050863265991</v>
+        <v>9.622881889343262</v>
       </c>
       <c r="C2" t="n">
-        <v>9.263819456100464</v>
+        <v>9.086646795272827</v>
       </c>
       <c r="D2" t="n">
-        <v>8.84679388999939</v>
+        <v>10.83861351013184</v>
       </c>
       <c r="E2" t="n">
-        <v>7.615947723388672</v>
+        <v>9.407379150390625</v>
       </c>
       <c r="F2" t="n">
-        <v>8.574412107467651</v>
+        <v>8.05146861076355</v>
       </c>
       <c r="G2" t="n">
-        <v>7.524765729904175</v>
+        <v>8.168319225311279</v>
       </c>
       <c r="H2" t="n">
-        <v>7.584863185882568</v>
+        <v>7.949741125106812</v>
       </c>
       <c r="I2" t="n">
-        <v>7.818494558334351</v>
+        <v>10.29746222496033</v>
       </c>
       <c r="J2" t="n">
-        <v>7.465023756027222</v>
+        <v>8.089366912841797</v>
       </c>
       <c r="K2" t="n">
-        <v>7.264458894729614</v>
+        <v>9.413840055465698</v>
       </c>
       <c r="L2" t="n">
-        <v>8.042463016510009</v>
+        <v>9.092571949958801</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.590508699417114</v>
+        <v>7.206727981567383</v>
       </c>
       <c r="C3" t="n">
-        <v>7.926964044570923</v>
+        <v>8.995942354202271</v>
       </c>
       <c r="D3" t="n">
-        <v>9.13487720489502</v>
+        <v>7.383256673812866</v>
       </c>
       <c r="E3" t="n">
-        <v>8.95728874206543</v>
+        <v>8.545148134231567</v>
       </c>
       <c r="F3" t="n">
-        <v>7.605466604232788</v>
+        <v>7.343361616134644</v>
       </c>
       <c r="G3" t="n">
-        <v>7.410678625106812</v>
+        <v>7.638221263885498</v>
       </c>
       <c r="H3" t="n">
-        <v>9.021856784820557</v>
+        <v>7.958347082138062</v>
       </c>
       <c r="I3" t="n">
-        <v>7.635001182556152</v>
+        <v>8.640891790390015</v>
       </c>
       <c r="J3" t="n">
-        <v>9.144684791564941</v>
+        <v>9.212364673614502</v>
       </c>
       <c r="K3" t="n">
-        <v>9.978960037231445</v>
+        <v>9.338027715682983</v>
       </c>
       <c r="L3" t="n">
-        <v>8.440628671646119</v>
+        <v>8.226228928565979</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.915635585784912</v>
+        <v>7.846018552780151</v>
       </c>
       <c r="C4" t="n">
-        <v>7.383500576019287</v>
+        <v>7.859980344772339</v>
       </c>
       <c r="D4" t="n">
-        <v>8.626330137252808</v>
+        <v>10.70360016822815</v>
       </c>
       <c r="E4" t="n">
-        <v>9.871636629104614</v>
+        <v>10.59535646438599</v>
       </c>
       <c r="F4" t="n">
-        <v>7.55787467956543</v>
+        <v>10.12195730209351</v>
       </c>
       <c r="G4" t="n">
-        <v>9.002357482910156</v>
+        <v>7.487072706222534</v>
       </c>
       <c r="H4" t="n">
-        <v>8.667789697647095</v>
+        <v>7.279550075531006</v>
       </c>
       <c r="I4" t="n">
-        <v>8.948983907699585</v>
+        <v>7.46403956413269</v>
       </c>
       <c r="J4" t="n">
-        <v>7.248516798019409</v>
+        <v>8.038407802581787</v>
       </c>
       <c r="K4" t="n">
-        <v>8.062499284744263</v>
+        <v>7.597682952880859</v>
       </c>
       <c r="L4" t="n">
-        <v>8.328512477874757</v>
+        <v>8.4993665933609</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7.997443437576294</v>
+        <v>7.287511825561523</v>
       </c>
       <c r="C5" t="n">
-        <v>6.755343675613403</v>
+        <v>8.969014644622803</v>
       </c>
       <c r="D5" t="n">
-        <v>7.596705675125122</v>
+        <v>8.060445308685303</v>
       </c>
       <c r="E5" t="n">
-        <v>6.943022727966309</v>
+        <v>6.830732583999634</v>
       </c>
       <c r="F5" t="n">
-        <v>8.245705842971802</v>
+        <v>7.13392162322998</v>
       </c>
       <c r="G5" t="n">
-        <v>7.370609760284424</v>
+        <v>7.023218631744385</v>
       </c>
       <c r="H5" t="n">
-        <v>8.985640048980713</v>
+        <v>7.394223928451538</v>
       </c>
       <c r="I5" t="n">
-        <v>7.015411376953125</v>
+        <v>8.235021114349365</v>
       </c>
       <c r="J5" t="n">
-        <v>7.270249843597412</v>
+        <v>9.152108907699585</v>
       </c>
       <c r="K5" t="n">
-        <v>7.002423048019409</v>
+        <v>7.263575792312622</v>
       </c>
       <c r="L5" t="n">
-        <v>7.518255543708801</v>
+        <v>7.734977436065674</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>7.5866539478302</v>
+        <v>7.640567064285278</v>
       </c>
       <c r="C6" t="n">
-        <v>7.659061193466187</v>
+        <v>7.480485916137695</v>
       </c>
       <c r="D6" t="n">
-        <v>7.301458120346069</v>
+        <v>7.357741832733154</v>
       </c>
       <c r="E6" t="n">
-        <v>8.017221212387085</v>
+        <v>7.888903856277466</v>
       </c>
       <c r="F6" t="n">
-        <v>8.105934619903564</v>
+        <v>7.086050271987915</v>
       </c>
       <c r="G6" t="n">
-        <v>7.565677404403687</v>
+        <v>7.352338552474976</v>
       </c>
       <c r="H6" t="n">
-        <v>7.673965215682983</v>
+        <v>6.919141530990601</v>
       </c>
       <c r="I6" t="n">
-        <v>7.668266534805298</v>
+        <v>6.786044359207153</v>
       </c>
       <c r="J6" t="n">
-        <v>7.472802639007568</v>
+        <v>7.963976860046387</v>
       </c>
       <c r="K6" t="n">
-        <v>8.166907787322998</v>
+        <v>7.463042736053467</v>
       </c>
       <c r="L6" t="n">
-        <v>7.721794867515564</v>
+        <v>7.393829298019409</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.541999816894531</v>
+        <v>7.513906717300415</v>
       </c>
       <c r="C7" t="n">
-        <v>7.611212730407715</v>
+        <v>7.472018480300903</v>
       </c>
       <c r="D7" t="n">
-        <v>8.147406339645386</v>
+        <v>7.733319520950317</v>
       </c>
       <c r="E7" t="n">
-        <v>7.549562931060791</v>
+        <v>8.04637622833252</v>
       </c>
       <c r="F7" t="n">
-        <v>8.654381513595581</v>
+        <v>7.516898393630981</v>
       </c>
       <c r="G7" t="n">
-        <v>7.755325555801392</v>
+        <v>8.151500225067139</v>
       </c>
       <c r="H7" t="n">
-        <v>8.246976613998413</v>
+        <v>8.371611833572388</v>
       </c>
       <c r="I7" t="n">
-        <v>7.435160875320435</v>
+        <v>8.418487548828125</v>
       </c>
       <c r="J7" t="n">
-        <v>7.700909852981567</v>
+        <v>7.995617866516113</v>
       </c>
       <c r="K7" t="n">
-        <v>8.279613494873047</v>
+        <v>7.96778678894043</v>
       </c>
       <c r="L7" t="n">
-        <v>7.992254972457886</v>
+        <v>7.918752360343933</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>8.84293270111084</v>
+        <v>7.369292497634888</v>
       </c>
       <c r="C8" t="n">
-        <v>7.155214071273804</v>
+        <v>7.391234397888184</v>
       </c>
       <c r="D8" t="n">
-        <v>7.248247861862183</v>
+        <v>7.181793928146362</v>
       </c>
       <c r="E8" t="n">
-        <v>8.546473264694214</v>
+        <v>7.703399658203125</v>
       </c>
       <c r="F8" t="n">
-        <v>8.268661260604858</v>
+        <v>7.655527114868164</v>
       </c>
       <c r="G8" t="n">
-        <v>9.020331144332886</v>
+        <v>7.557788848876953</v>
       </c>
       <c r="H8" t="n">
-        <v>9.535791873931885</v>
+        <v>7.18079686164856</v>
       </c>
       <c r="I8" t="n">
-        <v>7.837103128433228</v>
+        <v>9.7190101146698</v>
       </c>
       <c r="J8" t="n">
-        <v>7.582018136978149</v>
+        <v>7.730327129364014</v>
       </c>
       <c r="K8" t="n">
-        <v>9.398006677627563</v>
+        <v>7.57859206199646</v>
       </c>
       <c r="L8" t="n">
-        <v>8.343478012084962</v>
+        <v>7.706776261329651</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>8.536492586135864</v>
+        <v>8.288263082504272</v>
       </c>
       <c r="C9" t="n">
-        <v>7.52624773979187</v>
+        <v>8.12028431892395</v>
       </c>
       <c r="D9" t="n">
-        <v>7.39719820022583</v>
+        <v>8.228992938995361</v>
       </c>
       <c r="E9" t="n">
-        <v>7.516806840896606</v>
+        <v>8.175137758255005</v>
       </c>
       <c r="F9" t="n">
-        <v>7.73419189453125</v>
+        <v>7.620620965957642</v>
       </c>
       <c r="G9" t="n">
-        <v>7.778469085693359</v>
+        <v>8.75458836555481</v>
       </c>
       <c r="H9" t="n">
-        <v>7.983548879623413</v>
+        <v>8.292536735534668</v>
       </c>
       <c r="I9" t="n">
-        <v>9.635599613189697</v>
+        <v>8.017559289932251</v>
       </c>
       <c r="J9" t="n">
-        <v>9.145639181137085</v>
+        <v>8.167159795761108</v>
       </c>
       <c r="K9" t="n">
-        <v>8.494211912155151</v>
+        <v>8.158184051513672</v>
       </c>
       <c r="L9" t="n">
-        <v>8.174840593338013</v>
+        <v>8.182332730293274</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>7.126749277114868</v>
+        <v>8.111308336257935</v>
       </c>
       <c r="C10" t="n">
-        <v>7.211313962936401</v>
+        <v>7.600317716598511</v>
       </c>
       <c r="D10" t="n">
-        <v>7.546998739242554</v>
+        <v>7.127938747406006</v>
       </c>
       <c r="E10" t="n">
-        <v>6.732470512390137</v>
+        <v>6.993395328521729</v>
       </c>
       <c r="F10" t="n">
-        <v>6.947877168655396</v>
+        <v>7.581739664077759</v>
       </c>
       <c r="G10" t="n">
-        <v>7.063810110092163</v>
+        <v>7.041170120239258</v>
       </c>
       <c r="H10" t="n">
-        <v>7.144104242324829</v>
+        <v>6.856663227081299</v>
       </c>
       <c r="I10" t="n">
-        <v>7.43630051612854</v>
+        <v>7.040173292160034</v>
       </c>
       <c r="J10" t="n">
-        <v>6.802670478820801</v>
+        <v>7.482988595962524</v>
       </c>
       <c r="K10" t="n">
-        <v>8.037957429885864</v>
+        <v>6.979986429214478</v>
       </c>
       <c r="L10" t="n">
-        <v>7.205025243759155</v>
+        <v>7.281568145751953</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.201388597488403</v>
+        <v>7.45506477355957</v>
       </c>
       <c r="C11" t="n">
-        <v>6.87777853012085</v>
+        <v>9.126965045928955</v>
       </c>
       <c r="D11" t="n">
-        <v>6.589356422424316</v>
+        <v>8.02503228187561</v>
       </c>
       <c r="E11" t="n">
-        <v>6.557704210281372</v>
+        <v>8.697740077972412</v>
       </c>
       <c r="F11" t="n">
-        <v>6.556724309921265</v>
+        <v>8.778524398803711</v>
       </c>
       <c r="G11" t="n">
-        <v>7.447664022445679</v>
+        <v>9.204591512680054</v>
       </c>
       <c r="H11" t="n">
-        <v>6.390626192092896</v>
+        <v>9.034838914871216</v>
       </c>
       <c r="I11" t="n">
-        <v>7.517224311828613</v>
+        <v>8.481318950653076</v>
       </c>
       <c r="J11" t="n">
-        <v>7.986314296722412</v>
+        <v>11.40357685089111</v>
       </c>
       <c r="K11" t="n">
-        <v>6.934676885604858</v>
+        <v>7.069175243377686</v>
       </c>
       <c r="L11" t="n">
-        <v>7.005945777893066</v>
+        <v>8.72768280506134</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.121448993682861</v>
+        <v>8.949068307876587</v>
       </c>
       <c r="C12" t="n">
-        <v>6.48253870010376</v>
+        <v>8.575068473815918</v>
       </c>
       <c r="D12" t="n">
-        <v>7.377480983734131</v>
+        <v>7.842028141021729</v>
       </c>
       <c r="E12" t="n">
-        <v>7.219953536987305</v>
+        <v>8.855293750762939</v>
       </c>
       <c r="F12" t="n">
-        <v>7.517004251480103</v>
+        <v>8.643261432647705</v>
       </c>
       <c r="G12" t="n">
-        <v>8.472717761993408</v>
+        <v>7.917827606201172</v>
       </c>
       <c r="H12" t="n">
-        <v>7.639807462692261</v>
+        <v>7.579730033874512</v>
       </c>
       <c r="I12" t="n">
-        <v>7.401328802108765</v>
+        <v>7.467031478881836</v>
       </c>
       <c r="J12" t="n">
-        <v>8.603094577789307</v>
+        <v>7.292498350143433</v>
       </c>
       <c r="K12" t="n">
-        <v>8.893878698348999</v>
+        <v>8.779951810836792</v>
       </c>
       <c r="L12" t="n">
-        <v>7.67292537689209</v>
+        <v>8.190175938606263</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.371379375457764</v>
+        <v>9.462693214416504</v>
       </c>
       <c r="C13" t="n">
-        <v>6.715211391448975</v>
+        <v>7.040282249450684</v>
       </c>
       <c r="D13" t="n">
-        <v>6.637958288192749</v>
+        <v>7.006672620773315</v>
       </c>
       <c r="E13" t="n">
-        <v>7.215803861618042</v>
+        <v>7.119959831237793</v>
       </c>
       <c r="F13" t="n">
-        <v>6.8764328956604</v>
+        <v>6.41584300994873</v>
       </c>
       <c r="G13" t="n">
-        <v>6.73252272605896</v>
+        <v>6.915506601333618</v>
       </c>
       <c r="H13" t="n">
-        <v>7.191516160964966</v>
+        <v>6.988028287887573</v>
       </c>
       <c r="I13" t="n">
-        <v>7.352797031402588</v>
+        <v>7.063935041427612</v>
       </c>
       <c r="J13" t="n">
-        <v>7.144553422927856</v>
+        <v>7.264573574066162</v>
       </c>
       <c r="K13" t="n">
-        <v>8.763532638549805</v>
+        <v>8.019553661346436</v>
       </c>
       <c r="L13" t="n">
-        <v>7.200170779228211</v>
+        <v>7.329704809188843</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>8.07331109046936</v>
+        <v>8.549138784408569</v>
       </c>
       <c r="C14" t="n">
-        <v>7.871590375900269</v>
+        <v>7.816001176834106</v>
       </c>
       <c r="D14" t="n">
-        <v>8.430697917938232</v>
+        <v>8.52320671081543</v>
       </c>
       <c r="E14" t="n">
-        <v>7.708129644393921</v>
+        <v>7.746284961700439</v>
       </c>
       <c r="F14" t="n">
-        <v>7.783394336700439</v>
+        <v>11.41402244567871</v>
       </c>
       <c r="G14" t="n">
-        <v>8.49108624458313</v>
+        <v>9.456000089645386</v>
       </c>
       <c r="H14" t="n">
-        <v>10.63396406173706</v>
+        <v>8.680595397949219</v>
       </c>
       <c r="I14" t="n">
-        <v>8.142168760299683</v>
+        <v>8.097347974777222</v>
       </c>
       <c r="J14" t="n">
-        <v>8.285342693328857</v>
+        <v>8.279854774475098</v>
       </c>
       <c r="K14" t="n">
-        <v>10.06343293190002</v>
+        <v>8.180125713348389</v>
       </c>
       <c r="L14" t="n">
-        <v>8.548311805725097</v>
+        <v>8.674257802963258</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>9.985498428344727</v>
+        <v>9.738957166671753</v>
       </c>
       <c r="C15" t="n">
-        <v>7.704567670822144</v>
+        <v>8.170742273330688</v>
       </c>
       <c r="D15" t="n">
-        <v>10.24230170249939</v>
+        <v>10.13888716697693</v>
       </c>
       <c r="E15" t="n">
-        <v>9.158660411834717</v>
+        <v>8.999932050704956</v>
       </c>
       <c r="F15" t="n">
-        <v>8.738433599472046</v>
+        <v>9.199398756027222</v>
       </c>
       <c r="G15" t="n">
-        <v>8.804415225982666</v>
+        <v>10.32040071487427</v>
       </c>
       <c r="H15" t="n">
-        <v>8.037386178970337</v>
+        <v>10.487952709198</v>
       </c>
       <c r="I15" t="n">
-        <v>9.113072633743286</v>
+        <v>9.96235990524292</v>
       </c>
       <c r="J15" t="n">
-        <v>9.011298418045044</v>
+        <v>9.135569334030151</v>
       </c>
       <c r="K15" t="n">
-        <v>9.042800426483154</v>
+        <v>8.119426488876343</v>
       </c>
       <c r="L15" t="n">
-        <v>8.983843469619751</v>
+        <v>9.427362656593322</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.656126022338867</v>
+        <v>7.248620986938477</v>
       </c>
       <c r="C16" t="n">
-        <v>7.8193039894104</v>
+        <v>8.417482137680054</v>
       </c>
       <c r="D16" t="n">
-        <v>8.950043916702271</v>
+        <v>7.474084377288818</v>
       </c>
       <c r="E16" t="n">
-        <v>7.648473024368286</v>
+        <v>7.137911319732666</v>
       </c>
       <c r="F16" t="n">
-        <v>7.252060413360596</v>
+        <v>7.537750482559204</v>
       </c>
       <c r="G16" t="n">
-        <v>7.064785957336426</v>
+        <v>6.945832490921021</v>
       </c>
       <c r="H16" t="n">
-        <v>6.997710227966309</v>
+        <v>7.312444925308228</v>
       </c>
       <c r="I16" t="n">
-        <v>8.578685760498047</v>
+        <v>7.261689186096191</v>
       </c>
       <c r="J16" t="n">
-        <v>7.285768508911133</v>
+        <v>7.257591485977173</v>
       </c>
       <c r="K16" t="n">
-        <v>7.024993658065796</v>
+        <v>9.3958740234375</v>
       </c>
       <c r="L16" t="n">
-        <v>7.627795147895813</v>
+        <v>7.598928141593933</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>7.699800729751587</v>
+        <v>7.449079751968384</v>
       </c>
       <c r="C17" t="n">
-        <v>8.861408948898315</v>
+        <v>8.626930475234985</v>
       </c>
       <c r="D17" t="n">
-        <v>7.843559980392456</v>
+        <v>7.294493675231934</v>
       </c>
       <c r="E17" t="n">
-        <v>9.273482322692871</v>
+        <v>7.521884679794312</v>
       </c>
       <c r="F17" t="n">
-        <v>9.122299194335938</v>
+        <v>9.60331916809082</v>
       </c>
       <c r="G17" t="n">
-        <v>9.441885948181152</v>
+        <v>7.766231775283813</v>
       </c>
       <c r="H17" t="n">
-        <v>9.716451168060303</v>
+        <v>7.707388639450073</v>
       </c>
       <c r="I17" t="n">
-        <v>9.058378458023071</v>
+        <v>7.571826696395874</v>
       </c>
       <c r="J17" t="n">
-        <v>9.417965173721313</v>
+        <v>8.115784406661987</v>
       </c>
       <c r="K17" t="n">
-        <v>9.411257743835449</v>
+        <v>7.79656457901001</v>
       </c>
       <c r="L17" t="n">
-        <v>8.984648966789246</v>
+        <v>7.945350384712219</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>8.356953859329224</v>
+        <v>8.26589560508728</v>
       </c>
       <c r="C18" t="n">
-        <v>8.307490110397339</v>
+        <v>7.794628858566284</v>
       </c>
       <c r="D18" t="n">
-        <v>8.594865083694458</v>
+        <v>8.704721927642822</v>
       </c>
       <c r="E18" t="n">
-        <v>8.138735294342041</v>
+        <v>8.822375059127808</v>
       </c>
       <c r="F18" t="n">
-        <v>8.861062049865723</v>
+        <v>8.439430713653564</v>
       </c>
       <c r="G18" t="n">
-        <v>10.49136090278625</v>
+        <v>8.676796436309814</v>
       </c>
       <c r="H18" t="n">
-        <v>8.4868323802948</v>
+        <v>8.977991819381714</v>
       </c>
       <c r="I18" t="n">
-        <v>8.294149160385132</v>
+        <v>10.6295747756958</v>
       </c>
       <c r="J18" t="n">
-        <v>9.146920680999756</v>
+        <v>7.814416170120239</v>
       </c>
       <c r="K18" t="n">
-        <v>8.096641540527344</v>
+        <v>8.335179090499878</v>
       </c>
       <c r="L18" t="n">
-        <v>8.677501106262207</v>
+        <v>8.646101045608521</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.479750633239746</v>
+        <v>6.328570127487183</v>
       </c>
       <c r="C19" t="n">
-        <v>6.642003774642944</v>
+        <v>7.055699110031128</v>
       </c>
       <c r="D19" t="n">
-        <v>9.605102300643921</v>
+        <v>7.169826745986938</v>
       </c>
       <c r="E19" t="n">
-        <v>6.80439281463623</v>
+        <v>6.727011442184448</v>
       </c>
       <c r="F19" t="n">
-        <v>7.244752168655396</v>
+        <v>7.07807183265686</v>
       </c>
       <c r="G19" t="n">
-        <v>7.039464473724365</v>
+        <v>6.187324047088623</v>
       </c>
       <c r="H19" t="n">
-        <v>7.391730070114136</v>
+        <v>6.269235134124756</v>
       </c>
       <c r="I19" t="n">
-        <v>6.254653692245483</v>
+        <v>7.053138017654419</v>
       </c>
       <c r="J19" t="n">
-        <v>7.061337471008301</v>
+        <v>6.05879807472229</v>
       </c>
       <c r="K19" t="n">
-        <v>7.023979902267456</v>
+        <v>6.685778141021729</v>
       </c>
       <c r="L19" t="n">
-        <v>7.154716730117798</v>
+        <v>6.661345267295838</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.36153244972229</v>
+        <v>7.657522201538086</v>
       </c>
       <c r="C20" t="n">
-        <v>6.774152040481567</v>
+        <v>7.64672064781189</v>
       </c>
       <c r="D20" t="n">
-        <v>7.726930618286133</v>
+        <v>7.641021013259888</v>
       </c>
       <c r="E20" t="n">
-        <v>8.914438962936401</v>
+        <v>7.944296598434448</v>
       </c>
       <c r="F20" t="n">
-        <v>7.545133113861084</v>
+        <v>7.370803833007812</v>
       </c>
       <c r="G20" t="n">
-        <v>7.830606460571289</v>
+        <v>8.763563632965088</v>
       </c>
       <c r="H20" t="n">
-        <v>8.933144092559814</v>
+        <v>8.532543897628784</v>
       </c>
       <c r="I20" t="n">
-        <v>8.366826295852661</v>
+        <v>7.746285200119019</v>
       </c>
       <c r="J20" t="n">
-        <v>7.6658034324646</v>
+        <v>7.919820547103882</v>
       </c>
       <c r="K20" t="n">
-        <v>7.164759159088135</v>
+        <v>9.737959623336792</v>
       </c>
       <c r="L20" t="n">
-        <v>7.828332662582397</v>
+        <v>8.096053719520569</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>9.198730707168579</v>
+        <v>9.02486515045166</v>
       </c>
       <c r="C21" t="n">
-        <v>7.428053617477417</v>
+        <v>7.709382772445679</v>
       </c>
       <c r="D21" t="n">
-        <v>8.209226369857788</v>
+        <v>8.121282339096069</v>
       </c>
       <c r="E21" t="n">
-        <v>7.653613328933716</v>
+        <v>8.176135540008545</v>
       </c>
       <c r="F21" t="n">
-        <v>9.834663867950439</v>
+        <v>7.810113906860352</v>
       </c>
       <c r="G21" t="n">
-        <v>10.17998957633972</v>
+        <v>8.142225503921509</v>
       </c>
       <c r="H21" t="n">
-        <v>8.887179374694824</v>
+        <v>8.221015214920044</v>
       </c>
       <c r="I21" t="n">
-        <v>9.033408880233765</v>
+        <v>8.507249593734741</v>
       </c>
       <c r="J21" t="n">
-        <v>7.295608043670654</v>
+        <v>7.817844390869141</v>
       </c>
       <c r="K21" t="n">
-        <v>8.067121505737305</v>
+        <v>7.192765712738037</v>
       </c>
       <c r="L21" t="n">
-        <v>8.578759527206421</v>
+        <v>8.072288012504577</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>8.902338743209839</v>
+        <v>7.799144506454468</v>
       </c>
       <c r="C22" t="n">
-        <v>7.099632978439331</v>
+        <v>7.475009202957153</v>
       </c>
       <c r="D22" t="n">
-        <v>7.04855489730835</v>
+        <v>7.717253684997559</v>
       </c>
       <c r="E22" t="n">
-        <v>7.015914916992188</v>
+        <v>7.534837484359741</v>
       </c>
       <c r="F22" t="n">
-        <v>6.817345380783081</v>
+        <v>7.882809638977051</v>
       </c>
       <c r="G22" t="n">
-        <v>7.381414890289307</v>
+        <v>7.078504085540771</v>
       </c>
       <c r="H22" t="n">
-        <v>8.800140857696533</v>
+        <v>7.068824291229248</v>
       </c>
       <c r="I22" t="n">
-        <v>8.120615005493164</v>
+        <v>6.717169761657715</v>
       </c>
       <c r="J22" t="n">
-        <v>6.590724468231201</v>
+        <v>7.596891164779663</v>
       </c>
       <c r="K22" t="n">
-        <v>8.074950695037842</v>
+        <v>7.309575796127319</v>
       </c>
       <c r="L22" t="n">
-        <v>7.585163283348083</v>
+        <v>7.418001961708069</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.503772497177124</v>
+        <v>7.995779991149902</v>
       </c>
       <c r="C23" t="n">
-        <v>8.104803323745728</v>
+        <v>8.634184122085571</v>
       </c>
       <c r="D23" t="n">
-        <v>8.341835260391235</v>
+        <v>9.753154754638672</v>
       </c>
       <c r="E23" t="n">
-        <v>8.956750869750977</v>
+        <v>9.038495302200317</v>
       </c>
       <c r="F23" t="n">
-        <v>9.35485577583313</v>
+        <v>8.78457498550415</v>
       </c>
       <c r="G23" t="n">
-        <v>8.93306040763855</v>
+        <v>8.008094549179077</v>
       </c>
       <c r="H23" t="n">
-        <v>9.169082403182983</v>
+        <v>9.746273994445801</v>
       </c>
       <c r="I23" t="n">
-        <v>9.332434892654419</v>
+        <v>8.107211112976074</v>
       </c>
       <c r="J23" t="n">
-        <v>8.825550317764282</v>
+        <v>8.966632127761841</v>
       </c>
       <c r="K23" t="n">
-        <v>9.678867101669312</v>
+        <v>8.311198711395264</v>
       </c>
       <c r="L23" t="n">
-        <v>8.920101284980774</v>
+        <v>8.734559965133666</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.108536720275879</v>
+        <v>8.412444829940796</v>
       </c>
       <c r="C24" t="n">
-        <v>6.781527280807495</v>
+        <v>6.93362832069397</v>
       </c>
       <c r="D24" t="n">
-        <v>7.08049201965332</v>
+        <v>7.521945238113403</v>
       </c>
       <c r="E24" t="n">
-        <v>6.922913074493408</v>
+        <v>7.121360063552856</v>
       </c>
       <c r="F24" t="n">
-        <v>6.898131132125854</v>
+        <v>7.175961971282959</v>
       </c>
       <c r="G24" t="n">
-        <v>6.999013900756836</v>
+        <v>6.997784852981567</v>
       </c>
       <c r="H24" t="n">
-        <v>7.670369625091553</v>
+        <v>7.042823791503906</v>
       </c>
       <c r="I24" t="n">
-        <v>7.727508544921875</v>
+        <v>6.920773267745972</v>
       </c>
       <c r="J24" t="n">
-        <v>8.060553789138794</v>
+        <v>6.989887952804565</v>
       </c>
       <c r="K24" t="n">
-        <v>7.108093500137329</v>
+        <v>8.426138162612915</v>
       </c>
       <c r="L24" t="n">
-        <v>7.235713958740234</v>
+        <v>7.354274845123291</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>9.896499872207642</v>
+        <v>8.368768215179443</v>
       </c>
       <c r="C25" t="n">
-        <v>8.10742974281311</v>
+        <v>8.865705966949463</v>
       </c>
       <c r="D25" t="n">
-        <v>10.07760095596313</v>
+        <v>9.318914651870728</v>
       </c>
       <c r="E25" t="n">
-        <v>11.05974507331848</v>
+        <v>10.8847963809967</v>
       </c>
       <c r="F25" t="n">
-        <v>9.672013282775879</v>
+        <v>8.608473062515259</v>
       </c>
       <c r="G25" t="n">
-        <v>9.231149196624756</v>
+        <v>8.849099397659302</v>
       </c>
       <c r="H25" t="n">
-        <v>9.067321300506592</v>
+        <v>9.320704698562622</v>
       </c>
       <c r="I25" t="n">
-        <v>8.14384913444519</v>
+        <v>9.470851182937622</v>
       </c>
       <c r="J25" t="n">
-        <v>8.863837480545044</v>
+        <v>9.92154335975647</v>
       </c>
       <c r="K25" t="n">
-        <v>8.141675233840942</v>
+        <v>8.311563730239868</v>
       </c>
       <c r="L25" t="n">
-        <v>9.226112127304077</v>
+        <v>9.192042064666747</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>7.590011358261108</v>
+        <v>7.835035800933838</v>
       </c>
       <c r="C26" t="n">
-        <v>8.075403451919556</v>
+        <v>8.050802230834961</v>
       </c>
       <c r="D26" t="n">
-        <v>7.999320507049561</v>
+        <v>9.096384763717651</v>
       </c>
       <c r="E26" t="n">
-        <v>8.622956275939941</v>
+        <v>8.124766826629639</v>
       </c>
       <c r="F26" t="n">
-        <v>7.748463869094849</v>
+        <v>8.70706844329834</v>
       </c>
       <c r="G26" t="n">
-        <v>7.909955978393555</v>
+        <v>9.99403715133667</v>
       </c>
       <c r="H26" t="n">
-        <v>9.31173300743103</v>
+        <v>9.748608350753784</v>
       </c>
       <c r="I26" t="n">
-        <v>7.820887088775635</v>
+        <v>8.694242477416992</v>
       </c>
       <c r="J26" t="n">
-        <v>7.672341823577881</v>
+        <v>10.45788741111755</v>
       </c>
       <c r="K26" t="n">
-        <v>10.2319872379303</v>
+        <v>8.481746912002563</v>
       </c>
       <c r="L26" t="n">
-        <v>8.298306059837341</v>
+        <v>8.919058036804199</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>9.263180732727051</v>
+        <v>8.76308798789978</v>
       </c>
       <c r="C27" t="n">
-        <v>8.571290254592896</v>
+        <v>9.926128625869751</v>
       </c>
       <c r="D27" t="n">
-        <v>9.388099908828735</v>
+        <v>10.17141652107239</v>
       </c>
       <c r="E27" t="n">
-        <v>8.740716457366943</v>
+        <v>9.34899377822876</v>
       </c>
       <c r="F27" t="n">
-        <v>8.190210103988647</v>
+        <v>9.496300458908081</v>
       </c>
       <c r="G27" t="n">
-        <v>8.198466300964355</v>
+        <v>9.871967792510986</v>
       </c>
       <c r="H27" t="n">
-        <v>8.774980545043945</v>
+        <v>8.670524835586548</v>
       </c>
       <c r="I27" t="n">
-        <v>10.95610165596008</v>
+        <v>11.21479868888855</v>
       </c>
       <c r="J27" t="n">
-        <v>8.804841756820679</v>
+        <v>8.927150964736938</v>
       </c>
       <c r="K27" t="n">
-        <v>9.733563423156738</v>
+        <v>8.787362575531006</v>
       </c>
       <c r="L27" t="n">
-        <v>9.062145113945007</v>
+        <v>9.517773222923278</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>8.066450834274292</v>
+        <v>8.723560094833374</v>
       </c>
       <c r="C28" t="n">
-        <v>7.220044851303101</v>
+        <v>8.402945756912231</v>
       </c>
       <c r="D28" t="n">
-        <v>7.726826429367065</v>
+        <v>7.94457745552063</v>
       </c>
       <c r="E28" t="n">
-        <v>8.47412896156311</v>
+        <v>7.941392660140991</v>
       </c>
       <c r="F28" t="n">
-        <v>7.529058218002319</v>
+        <v>8.46185302734375</v>
       </c>
       <c r="G28" t="n">
-        <v>7.983503103256226</v>
+        <v>7.801533699035645</v>
       </c>
       <c r="H28" t="n">
-        <v>8.395476341247559</v>
+        <v>7.705359220504761</v>
       </c>
       <c r="I28" t="n">
-        <v>7.295315742492676</v>
+        <v>7.743613958358765</v>
       </c>
       <c r="J28" t="n">
-        <v>8.474875211715698</v>
+        <v>7.994824886322021</v>
       </c>
       <c r="K28" t="n">
-        <v>7.757615327835083</v>
+        <v>8.210028886795044</v>
       </c>
       <c r="L28" t="n">
-        <v>7.892329502105713</v>
+        <v>8.092968964576722</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>8.277618408203125</v>
+        <v>8.035262584686279</v>
       </c>
       <c r="C29" t="n">
-        <v>6.992986917495728</v>
+        <v>8.066027641296387</v>
       </c>
       <c r="D29" t="n">
-        <v>8.474298715591431</v>
+        <v>8.483742713928223</v>
       </c>
       <c r="E29" t="n">
-        <v>7.501479625701904</v>
+        <v>8.077408313751221</v>
       </c>
       <c r="F29" t="n">
-        <v>8.280675649642944</v>
+        <v>8.051438808441162</v>
       </c>
       <c r="G29" t="n">
-        <v>7.182887315750122</v>
+        <v>8.001511335372925</v>
       </c>
       <c r="H29" t="n">
-        <v>9.140379428863525</v>
+        <v>7.670346260070801</v>
       </c>
       <c r="I29" t="n">
-        <v>7.552770376205444</v>
+        <v>8.142389059066772</v>
       </c>
       <c r="J29" t="n">
-        <v>8.647877216339111</v>
+        <v>8.136492490768433</v>
       </c>
       <c r="K29" t="n">
-        <v>8.200438022613525</v>
+        <v>8.435260057449341</v>
       </c>
       <c r="L29" t="n">
-        <v>8.025141167640687</v>
+        <v>8.109987926483154</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.029576301574707</v>
+        <v>8.022588729858398</v>
       </c>
       <c r="C30" t="n">
-        <v>7.326092720031738</v>
+        <v>7.958563327789307</v>
       </c>
       <c r="D30" t="n">
-        <v>7.226557970046997</v>
+        <v>7.551765441894531</v>
       </c>
       <c r="E30" t="n">
-        <v>7.121357202529907</v>
+        <v>8.003950595855713</v>
       </c>
       <c r="F30" t="n">
-        <v>7.006873846054077</v>
+        <v>8.396218299865723</v>
       </c>
       <c r="G30" t="n">
-        <v>7.337198257446289</v>
+        <v>8.604554414749146</v>
       </c>
       <c r="H30" t="n">
-        <v>8.091337919235229</v>
+        <v>9.110725164413452</v>
       </c>
       <c r="I30" t="n">
-        <v>7.880712270736694</v>
+        <v>8.079303741455078</v>
       </c>
       <c r="J30" t="n">
-        <v>7.309086561203003</v>
+        <v>7.944766759872437</v>
       </c>
       <c r="K30" t="n">
-        <v>8.736687660217285</v>
+        <v>7.496300458908081</v>
       </c>
       <c r="L30" t="n">
-        <v>7.506548070907593</v>
+        <v>8.116873693466186</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>7.357351303100586</v>
+        <v>7.685645341873169</v>
       </c>
       <c r="C31" t="n">
-        <v>7.294106721878052</v>
+        <v>8.078639984130859</v>
       </c>
       <c r="D31" t="n">
-        <v>8.206868410110474</v>
+        <v>8.188661098480225</v>
       </c>
       <c r="E31" t="n">
-        <v>8.179502487182617</v>
+        <v>8.73150634765625</v>
       </c>
       <c r="F31" t="n">
-        <v>7.406143188476562</v>
+        <v>11.98207211494446</v>
       </c>
       <c r="G31" t="n">
-        <v>7.647103548049927</v>
+        <v>8.863864421844482</v>
       </c>
       <c r="H31" t="n">
-        <v>7.06164813041687</v>
+        <v>10.30741620063782</v>
       </c>
       <c r="I31" t="n">
-        <v>7.134212017059326</v>
+        <v>9.37063455581665</v>
       </c>
       <c r="J31" t="n">
-        <v>6.955546140670776</v>
+        <v>7.878030061721802</v>
       </c>
       <c r="K31" t="n">
-        <v>6.575303077697754</v>
+        <v>9.983673095703125</v>
       </c>
       <c r="L31" t="n">
-        <v>7.381778502464295</v>
+        <v>9.107014322280884</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.090121269226074</v>
+        <v>9.441604137420654</v>
       </c>
       <c r="C32" t="n">
-        <v>10.86901998519897</v>
+        <v>9.852413654327393</v>
       </c>
       <c r="D32" t="n">
-        <v>9.818053245544434</v>
+        <v>10.5178816318512</v>
       </c>
       <c r="E32" t="n">
-        <v>10.51522874832153</v>
+        <v>10.413170337677</v>
       </c>
       <c r="F32" t="n">
-        <v>9.304939746856689</v>
+        <v>8.295410633087158</v>
       </c>
       <c r="G32" t="n">
-        <v>9.339268445968628</v>
+        <v>10.26513600349426</v>
       </c>
       <c r="H32" t="n">
-        <v>10.18442177772522</v>
+        <v>10.56068181991577</v>
       </c>
       <c r="I32" t="n">
-        <v>7.694441556930542</v>
+        <v>9.895752191543579</v>
       </c>
       <c r="J32" t="n">
-        <v>8.563110589981079</v>
+        <v>9.650454521179199</v>
       </c>
       <c r="K32" t="n">
-        <v>9.225802659988403</v>
+        <v>9.816646575927734</v>
       </c>
       <c r="L32" t="n">
-        <v>9.360440802574157</v>
+        <v>9.870915150642395</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>9.265567541122437</v>
+        <v>8.430566310882568</v>
       </c>
       <c r="C33" t="n">
-        <v>7.794394493103027</v>
+        <v>7.500824451446533</v>
       </c>
       <c r="D33" t="n">
-        <v>7.922013521194458</v>
+        <v>8.502147674560547</v>
       </c>
       <c r="E33" t="n">
-        <v>8.362342357635498</v>
+        <v>7.584506750106812</v>
       </c>
       <c r="F33" t="n">
-        <v>7.959563732147217</v>
+        <v>8.41963529586792</v>
       </c>
       <c r="G33" t="n">
-        <v>8.166868209838867</v>
+        <v>25.20566606521606</v>
       </c>
       <c r="H33" t="n">
-        <v>7.511224746704102</v>
+        <v>8.302637338638306</v>
       </c>
       <c r="I33" t="n">
-        <v>7.864471912384033</v>
+        <v>8.105282545089722</v>
       </c>
       <c r="J33" t="n">
-        <v>8.200859785079956</v>
+        <v>8.036084890365601</v>
       </c>
       <c r="K33" t="n">
-        <v>7.08164644241333</v>
+        <v>8.26772141456604</v>
       </c>
       <c r="L33" t="n">
-        <v>8.012895274162293</v>
+        <v>9.835507273674011</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>7.343582391738892</v>
+        <v>8.835125684738159</v>
       </c>
       <c r="C34" t="n">
-        <v>7.904321432113647</v>
+        <v>8.464779376983643</v>
       </c>
       <c r="D34" t="n">
-        <v>8.635670900344849</v>
+        <v>8.656007528305054</v>
       </c>
       <c r="E34" t="n">
-        <v>9.21854567527771</v>
+        <v>7.994045734405518</v>
       </c>
       <c r="F34" t="n">
-        <v>7.980541706085205</v>
+        <v>7.979638576507568</v>
       </c>
       <c r="G34" t="n">
-        <v>7.687775850296021</v>
+        <v>7.774199962615967</v>
       </c>
       <c r="H34" t="n">
-        <v>7.984098196029663</v>
+        <v>8.163025856018066</v>
       </c>
       <c r="I34" t="n">
-        <v>7.833441734313965</v>
+        <v>8.281321287155151</v>
       </c>
       <c r="J34" t="n">
-        <v>7.232060432434082</v>
+        <v>7.582435846328735</v>
       </c>
       <c r="K34" t="n">
-        <v>8.071984767913818</v>
+        <v>8.058894395828247</v>
       </c>
       <c r="L34" t="n">
-        <v>7.989202308654785</v>
+        <v>8.17894742488861</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.586445093154907</v>
+        <v>7.269462108612061</v>
       </c>
       <c r="C35" t="n">
-        <v>7.479982852935791</v>
+        <v>7.038197994232178</v>
       </c>
       <c r="D35" t="n">
-        <v>7.492009162902832</v>
+        <v>7.185549736022949</v>
       </c>
       <c r="E35" t="n">
-        <v>8.378368854522705</v>
+        <v>7.36042046546936</v>
       </c>
       <c r="F35" t="n">
-        <v>8.168681144714355</v>
+        <v>6.926289319992065</v>
       </c>
       <c r="G35" t="n">
-        <v>7.920850515365601</v>
+        <v>7.433377742767334</v>
       </c>
       <c r="H35" t="n">
-        <v>7.376685857772827</v>
+        <v>7.544584512710571</v>
       </c>
       <c r="I35" t="n">
-        <v>7.295802354812622</v>
+        <v>7.213613986968994</v>
       </c>
       <c r="J35" t="n">
-        <v>7.701917171478271</v>
+        <v>7.191119194030762</v>
       </c>
       <c r="K35" t="n">
-        <v>7.919120311737061</v>
+        <v>7.173129796981812</v>
       </c>
       <c r="L35" t="n">
-        <v>7.731986331939697</v>
+        <v>7.233574485778808</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.85358738899231</v>
+        <v>8.000102758407593</v>
       </c>
       <c r="C36" t="n">
-        <v>8.693545579910278</v>
+        <v>8.930906772613525</v>
       </c>
       <c r="D36" t="n">
-        <v>7.157630681991577</v>
+        <v>7.925800800323486</v>
       </c>
       <c r="E36" t="n">
-        <v>8.505872011184692</v>
+        <v>7.396878480911255</v>
       </c>
       <c r="F36" t="n">
-        <v>9.092728853225708</v>
+        <v>8.311511516571045</v>
       </c>
       <c r="G36" t="n">
-        <v>7.327021360397339</v>
+        <v>8.809455871582031</v>
       </c>
       <c r="H36" t="n">
-        <v>8.841688632965088</v>
+        <v>8.200803756713867</v>
       </c>
       <c r="I36" t="n">
-        <v>8.356326341629028</v>
+        <v>8.358140230178833</v>
       </c>
       <c r="J36" t="n">
-        <v>8.989728689193726</v>
+        <v>8.547595262527466</v>
       </c>
       <c r="K36" t="n">
-        <v>8.71983003616333</v>
+        <v>7.497783422470093</v>
       </c>
       <c r="L36" t="n">
-        <v>8.453795957565308</v>
+        <v>8.197897887229919</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>8.785374164581299</v>
+        <v>7.54151725769043</v>
       </c>
       <c r="C37" t="n">
-        <v>7.892711400985718</v>
+        <v>6.740486621856689</v>
       </c>
       <c r="D37" t="n">
-        <v>7.421906232833862</v>
+        <v>6.644253969192505</v>
       </c>
       <c r="E37" t="n">
-        <v>9.061908483505249</v>
+        <v>6.828932285308838</v>
       </c>
       <c r="F37" t="n">
-        <v>7.034783840179443</v>
+        <v>7.039529800415039</v>
       </c>
       <c r="G37" t="n">
-        <v>7.865680694580078</v>
+        <v>7.163416862487793</v>
       </c>
       <c r="H37" t="n">
-        <v>7.112369775772095</v>
+        <v>7.381754875183105</v>
       </c>
       <c r="I37" t="n">
-        <v>7.160158395767212</v>
+        <v>7.075803995132446</v>
       </c>
       <c r="J37" t="n">
-        <v>7.279838562011719</v>
+        <v>6.97226881980896</v>
       </c>
       <c r="K37" t="n">
-        <v>7.090503931045532</v>
+        <v>7.445812940597534</v>
       </c>
       <c r="L37" t="n">
-        <v>7.670523548126221</v>
+        <v>7.083377742767334</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>7.191719055175781</v>
+        <v>6.770950794219971</v>
       </c>
       <c r="C38" t="n">
-        <v>7.307159662246704</v>
+        <v>7.283696174621582</v>
       </c>
       <c r="D38" t="n">
-        <v>8.409837484359741</v>
+        <v>6.921185493469238</v>
       </c>
       <c r="E38" t="n">
-        <v>7.627584934234619</v>
+        <v>7.165290355682373</v>
       </c>
       <c r="F38" t="n">
-        <v>7.43256950378418</v>
+        <v>7.229225873947144</v>
       </c>
       <c r="G38" t="n">
-        <v>7.858216285705566</v>
+        <v>7.160874605178833</v>
       </c>
       <c r="H38" t="n">
-        <v>6.933622360229492</v>
+        <v>6.958556175231934</v>
       </c>
       <c r="I38" t="n">
-        <v>7.414589405059814</v>
+        <v>6.789664745330811</v>
       </c>
       <c r="J38" t="n">
-        <v>7.877795934677124</v>
+        <v>7.01404881477356</v>
       </c>
       <c r="K38" t="n">
-        <v>7.902784585952759</v>
+        <v>7.21049427986145</v>
       </c>
       <c r="L38" t="n">
-        <v>7.595587921142578</v>
+        <v>7.05039873123169</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>7.404206037521362</v>
+        <v>7.474807500839233</v>
       </c>
       <c r="C39" t="n">
-        <v>8.253314971923828</v>
+        <v>7.43210768699646</v>
       </c>
       <c r="D39" t="n">
-        <v>6.96665620803833</v>
+        <v>8.172175884246826</v>
       </c>
       <c r="E39" t="n">
-        <v>8.378437995910645</v>
+        <v>7.221004247665405</v>
       </c>
       <c r="F39" t="n">
-        <v>7.277941465377808</v>
+        <v>7.222002506256104</v>
       </c>
       <c r="G39" t="n">
-        <v>7.673353672027588</v>
+        <v>7.298287153244019</v>
       </c>
       <c r="H39" t="n">
-        <v>7.480782032012939</v>
+        <v>7.551539421081543</v>
       </c>
       <c r="I39" t="n">
-        <v>7.380064249038696</v>
+        <v>7.624259471893311</v>
       </c>
       <c r="J39" t="n">
-        <v>7.050862789154053</v>
+        <v>7.228210687637329</v>
       </c>
       <c r="K39" t="n">
-        <v>7.366743326187134</v>
+        <v>7.203949213027954</v>
       </c>
       <c r="L39" t="n">
-        <v>7.523236274719238</v>
+        <v>7.442834377288818</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.061368465423584</v>
+        <v>7.3262038230896</v>
       </c>
       <c r="C40" t="n">
-        <v>7.072845697402954</v>
+        <v>7.201292991638184</v>
       </c>
       <c r="D40" t="n">
-        <v>7.07600474357605</v>
+        <v>7.856033325195312</v>
       </c>
       <c r="E40" t="n">
-        <v>7.329250574111938</v>
+        <v>7.50700855255127</v>
       </c>
       <c r="F40" t="n">
-        <v>6.860313415527344</v>
+        <v>8.743929862976074</v>
       </c>
       <c r="G40" t="n">
-        <v>7.527740716934204</v>
+        <v>7.101658582687378</v>
       </c>
       <c r="H40" t="n">
-        <v>8.016239404678345</v>
+        <v>7.43332839012146</v>
       </c>
       <c r="I40" t="n">
-        <v>7.29460597038269</v>
+        <v>8.217412948608398</v>
       </c>
       <c r="J40" t="n">
-        <v>6.975471496582031</v>
+        <v>7.037850618362427</v>
       </c>
       <c r="K40" t="n">
-        <v>8.809994459152222</v>
+        <v>7.154776811599731</v>
       </c>
       <c r="L40" t="n">
-        <v>7.402383494377136</v>
+        <v>7.557949590682983</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.378553152084351</v>
+        <v>7.371674776077271</v>
       </c>
       <c r="C41" t="n">
-        <v>6.926181554794312</v>
+        <v>6.880767583847046</v>
       </c>
       <c r="D41" t="n">
-        <v>8.070476055145264</v>
+        <v>7.649490833282471</v>
       </c>
       <c r="E41" t="n">
-        <v>8.827653884887695</v>
+        <v>7.06287407875061</v>
       </c>
       <c r="F41" t="n">
-        <v>8.791215419769287</v>
+        <v>7.177168607711792</v>
       </c>
       <c r="G41" t="n">
-        <v>7.329668760299683</v>
+        <v>7.20690655708313</v>
       </c>
       <c r="H41" t="n">
-        <v>7.034906148910522</v>
+        <v>6.987800121307373</v>
       </c>
       <c r="I41" t="n">
-        <v>7.279017686843872</v>
+        <v>6.521304607391357</v>
       </c>
       <c r="J41" t="n">
-        <v>7.674412727355957</v>
+        <v>7.669635534286499</v>
       </c>
       <c r="K41" t="n">
-        <v>6.963533639907837</v>
+        <v>8.424592018127441</v>
       </c>
       <c r="L41" t="n">
-        <v>7.627561902999878</v>
+        <v>7.295221471786499</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>8.835531949996948</v>
+        <v>7.539365768432617</v>
       </c>
       <c r="C42" t="n">
-        <v>9.071625709533691</v>
+        <v>7.180114269256592</v>
       </c>
       <c r="D42" t="n">
-        <v>8.501973390579224</v>
+        <v>7.383395433425903</v>
       </c>
       <c r="E42" t="n">
-        <v>8.797914028167725</v>
+        <v>7.352938413619995</v>
       </c>
       <c r="F42" t="n">
-        <v>6.743137359619141</v>
+        <v>7.013165950775146</v>
       </c>
       <c r="G42" t="n">
-        <v>8.154457092285156</v>
+        <v>6.967056512832642</v>
       </c>
       <c r="H42" t="n">
-        <v>7.541208028793335</v>
+        <v>7.245991468429565</v>
       </c>
       <c r="I42" t="n">
-        <v>7.388622760772705</v>
+        <v>6.971039056777954</v>
       </c>
       <c r="J42" t="n">
-        <v>7.196466684341431</v>
+        <v>7.374624252319336</v>
       </c>
       <c r="K42" t="n">
-        <v>7.993816375732422</v>
+        <v>7.092041492462158</v>
       </c>
       <c r="L42" t="n">
-        <v>8.022475337982177</v>
+        <v>7.211973261833191</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.196480512619019</v>
+        <v>7.668721675872803</v>
       </c>
       <c r="C43" t="n">
-        <v>9.086516141891479</v>
+        <v>7.588414669036865</v>
       </c>
       <c r="D43" t="n">
-        <v>7.496902465820312</v>
+        <v>7.446932554244995</v>
       </c>
       <c r="E43" t="n">
-        <v>7.449476003646851</v>
+        <v>7.629782199859619</v>
       </c>
       <c r="F43" t="n">
-        <v>6.826964139938354</v>
+        <v>7.461271286010742</v>
       </c>
       <c r="G43" t="n">
-        <v>6.989990472793579</v>
+        <v>9.66723108291626</v>
       </c>
       <c r="H43" t="n">
-        <v>6.67305588722229</v>
+        <v>7.355144739151001</v>
       </c>
       <c r="I43" t="n">
-        <v>8.69012451171875</v>
+        <v>7.623721122741699</v>
       </c>
       <c r="J43" t="n">
-        <v>8.746962547302246</v>
+        <v>8.502444505691528</v>
       </c>
       <c r="K43" t="n">
-        <v>7.262201309204102</v>
+        <v>7.028908967971802</v>
       </c>
       <c r="L43" t="n">
-        <v>7.641867399215698</v>
+        <v>7.797257280349731</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.775056600570679</v>
+        <v>6.178403854370117</v>
       </c>
       <c r="C44" t="n">
-        <v>6.62489128112793</v>
+        <v>6.312622308731079</v>
       </c>
       <c r="D44" t="n">
-        <v>6.691077709197998</v>
+        <v>6.465658664703369</v>
       </c>
       <c r="E44" t="n">
-        <v>7.122821092605591</v>
+        <v>6.410083770751953</v>
       </c>
       <c r="F44" t="n">
-        <v>7.334804773330688</v>
+        <v>6.467134475708008</v>
       </c>
       <c r="G44" t="n">
-        <v>6.751441717147827</v>
+        <v>6.332161664962769</v>
       </c>
       <c r="H44" t="n">
-        <v>6.618315458297729</v>
+        <v>6.624064683914185</v>
       </c>
       <c r="I44" t="n">
-        <v>6.961729288101196</v>
+        <v>6.250295877456665</v>
       </c>
       <c r="J44" t="n">
-        <v>6.928293704986572</v>
+        <v>6.610469102859497</v>
       </c>
       <c r="K44" t="n">
-        <v>7.460219383239746</v>
+        <v>6.752768516540527</v>
       </c>
       <c r="L44" t="n">
-        <v>6.926865100860596</v>
+        <v>6.440366291999817</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>7.882968187332153</v>
+        <v>9.259482622146606</v>
       </c>
       <c r="C45" t="n">
-        <v>8.568707704544067</v>
+        <v>8.367672204971313</v>
       </c>
       <c r="D45" t="n">
-        <v>8.048993110656738</v>
+        <v>8.202553749084473</v>
       </c>
       <c r="E45" t="n">
-        <v>8.188332080841064</v>
+        <v>9.272229909896851</v>
       </c>
       <c r="F45" t="n">
-        <v>8.193871974945068</v>
+        <v>8.741929769515991</v>
       </c>
       <c r="G45" t="n">
-        <v>8.266711950302124</v>
+        <v>8.285639047622681</v>
       </c>
       <c r="H45" t="n">
-        <v>9.9117271900177</v>
+        <v>8.190538644790649</v>
       </c>
       <c r="I45" t="n">
-        <v>8.430049180984497</v>
+        <v>7.732905387878418</v>
       </c>
       <c r="J45" t="n">
-        <v>8.48663592338562</v>
+        <v>8.448220491409302</v>
       </c>
       <c r="K45" t="n">
-        <v>9.589975357055664</v>
+        <v>8.349009990692139</v>
       </c>
       <c r="L45" t="n">
-        <v>8.55679726600647</v>
+        <v>8.485018181800843</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>6.736852884292603</v>
+        <v>6.937255382537842</v>
       </c>
       <c r="C46" t="n">
-        <v>7.105817079544067</v>
+        <v>8.600418329238892</v>
       </c>
       <c r="D46" t="n">
-        <v>7.946759700775146</v>
+        <v>7.236415147781372</v>
       </c>
       <c r="E46" t="n">
-        <v>8.197339773178101</v>
+        <v>7.150018692016602</v>
       </c>
       <c r="F46" t="n">
-        <v>7.607497453689575</v>
+        <v>6.687348127365112</v>
       </c>
       <c r="G46" t="n">
-        <v>8.303007841110229</v>
+        <v>6.687757015228271</v>
       </c>
       <c r="H46" t="n">
-        <v>8.168806314468384</v>
+        <v>6.981359720230103</v>
       </c>
       <c r="I46" t="n">
-        <v>7.275486469268799</v>
+        <v>7.282671928405762</v>
       </c>
       <c r="J46" t="n">
-        <v>7.084842681884766</v>
+        <v>6.538677930831909</v>
       </c>
       <c r="K46" t="n">
-        <v>8.170625686645508</v>
+        <v>7.121274471282959</v>
       </c>
       <c r="L46" t="n">
-        <v>7.659703588485717</v>
+        <v>7.122319674491882</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.906085729598999</v>
+        <v>7.647924661636353</v>
       </c>
       <c r="C47" t="n">
-        <v>9.286628246307373</v>
+        <v>8.198595762252808</v>
       </c>
       <c r="D47" t="n">
-        <v>9.998472690582275</v>
+        <v>7.7034752368927</v>
       </c>
       <c r="E47" t="n">
-        <v>7.907694101333618</v>
+        <v>8.111781358718872</v>
       </c>
       <c r="F47" t="n">
-        <v>8.962704181671143</v>
+        <v>8.621087551116943</v>
       </c>
       <c r="G47" t="n">
-        <v>10.09642314910889</v>
+        <v>7.912151575088501</v>
       </c>
       <c r="H47" t="n">
-        <v>8.066304683685303</v>
+        <v>8.4217689037323</v>
       </c>
       <c r="I47" t="n">
-        <v>8.050144672393799</v>
+        <v>7.858566522598267</v>
       </c>
       <c r="J47" t="n">
-        <v>7.684274196624756</v>
+        <v>8.353159189224243</v>
       </c>
       <c r="K47" t="n">
-        <v>7.561025381088257</v>
+        <v>7.738649368286133</v>
       </c>
       <c r="L47" t="n">
-        <v>8.65197570323944</v>
+        <v>8.056716012954713</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.71414041519165</v>
+        <v>7.011410474777222</v>
       </c>
       <c r="C48" t="n">
-        <v>8.028472900390625</v>
+        <v>7.188634634017944</v>
       </c>
       <c r="D48" t="n">
-        <v>6.742459058761597</v>
+        <v>6.649732112884521</v>
       </c>
       <c r="E48" t="n">
-        <v>6.554736375808716</v>
+        <v>6.625488996505737</v>
       </c>
       <c r="F48" t="n">
-        <v>7.714838027954102</v>
+        <v>6.76538610458374</v>
       </c>
       <c r="G48" t="n">
-        <v>6.874415159225464</v>
+        <v>6.369829893112183</v>
       </c>
       <c r="H48" t="n">
-        <v>7.396034955978394</v>
+        <v>8.239883184432983</v>
       </c>
       <c r="I48" t="n">
-        <v>6.48677134513855</v>
+        <v>6.505708932876587</v>
       </c>
       <c r="J48" t="n">
-        <v>6.938729524612427</v>
+        <v>6.585585355758667</v>
       </c>
       <c r="K48" t="n">
-        <v>7.171191930770874</v>
+        <v>7.064205646514893</v>
       </c>
       <c r="L48" t="n">
-        <v>7.06217896938324</v>
+        <v>6.900586533546448</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>8.201419353485107</v>
+        <v>7.13701605796814</v>
       </c>
       <c r="C49" t="n">
-        <v>7.106626272201538</v>
+        <v>7.896032810211182</v>
       </c>
       <c r="D49" t="n">
-        <v>7.671378612518311</v>
+        <v>6.878382682800293</v>
       </c>
       <c r="E49" t="n">
-        <v>7.217118263244629</v>
+        <v>7.061331987380981</v>
       </c>
       <c r="F49" t="n">
-        <v>7.353945732116699</v>
+        <v>7.427012920379639</v>
       </c>
       <c r="G49" t="n">
-        <v>7.12014102935791</v>
+        <v>6.709969043731689</v>
       </c>
       <c r="H49" t="n">
-        <v>7.141567230224609</v>
+        <v>6.922742605209351</v>
       </c>
       <c r="I49" t="n">
-        <v>7.214561223983765</v>
+        <v>7.132911443710327</v>
       </c>
       <c r="J49" t="n">
-        <v>7.561354875564575</v>
+        <v>7.224497318267822</v>
       </c>
       <c r="K49" t="n">
-        <v>6.915186405181885</v>
+        <v>7.479159116744995</v>
       </c>
       <c r="L49" t="n">
-        <v>7.350329899787903</v>
+        <v>7.186905598640442</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>7.444105863571167</v>
+        <v>8.104393005371094</v>
       </c>
       <c r="C50" t="n">
-        <v>9.095390319824219</v>
+        <v>7.370625019073486</v>
       </c>
       <c r="D50" t="n">
-        <v>7.929265022277832</v>
+        <v>7.596207141876221</v>
       </c>
       <c r="E50" t="n">
-        <v>9.047153949737549</v>
+        <v>7.301246881484985</v>
       </c>
       <c r="F50" t="n">
-        <v>7.712647676467896</v>
+        <v>7.248177289962769</v>
       </c>
       <c r="G50" t="n">
-        <v>8.690466403961182</v>
+        <v>7.412483692169189</v>
       </c>
       <c r="H50" t="n">
-        <v>7.644930362701416</v>
+        <v>7.67905592918396</v>
       </c>
       <c r="I50" t="n">
-        <v>8.200732231140137</v>
+        <v>8.88900899887085</v>
       </c>
       <c r="J50" t="n">
-        <v>7.672672986984253</v>
+        <v>7.187082290649414</v>
       </c>
       <c r="K50" t="n">
-        <v>8.810803890228271</v>
+        <v>7.024338722229004</v>
       </c>
       <c r="L50" t="n">
-        <v>8.224816870689391</v>
+        <v>7.581261897087098</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>6.836867809295654</v>
+        <v>6.701478958129883</v>
       </c>
       <c r="C51" t="n">
-        <v>6.948477029800415</v>
+        <v>6.829321384429932</v>
       </c>
       <c r="D51" t="n">
-        <v>7.245971918106079</v>
+        <v>6.973323345184326</v>
       </c>
       <c r="E51" t="n">
-        <v>6.633905649185181</v>
+        <v>7.91221022605896</v>
       </c>
       <c r="F51" t="n">
-        <v>6.930269479751587</v>
+        <v>6.529342174530029</v>
       </c>
       <c r="G51" t="n">
-        <v>7.490808963775635</v>
+        <v>7.207480669021606</v>
       </c>
       <c r="H51" t="n">
-        <v>8.192146301269531</v>
+        <v>6.82039213180542</v>
       </c>
       <c r="I51" t="n">
-        <v>6.709927558898926</v>
+        <v>6.949665546417236</v>
       </c>
       <c r="J51" t="n">
-        <v>6.588439226150513</v>
+        <v>6.610238552093506</v>
       </c>
       <c r="K51" t="n">
-        <v>6.963477849960327</v>
+        <v>6.526108503341675</v>
       </c>
       <c r="L51" t="n">
-        <v>7.054029178619385</v>
+        <v>6.905956149101257</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.911915168762207</v>
+        <v>7.906094794273376</v>
       </c>
       <c r="C52" t="n">
-        <v>7.733334503173828</v>
+        <v>7.924107761383056</v>
       </c>
       <c r="D52" t="n">
-        <v>8.017350134849549</v>
+        <v>8.017427577972413</v>
       </c>
       <c r="E52" t="n">
-        <v>8.079219355583191</v>
+        <v>7.962068119049072</v>
       </c>
       <c r="F52" t="n">
-        <v>7.864283919334412</v>
+        <v>8.005101079940795</v>
       </c>
       <c r="G52" t="n">
-        <v>7.974531707763671</v>
+        <v>8.250244193077087</v>
       </c>
       <c r="H52" t="n">
-        <v>8.1292697763443</v>
+        <v>7.959032769203186</v>
       </c>
       <c r="I52" t="n">
-        <v>7.869769821166992</v>
+        <v>8.004009695053101</v>
       </c>
       <c r="J52" t="n">
-        <v>7.8275297498703</v>
+        <v>7.94742913722992</v>
       </c>
       <c r="K52" t="n">
-        <v>8.129235253334045</v>
+        <v>7.905123734474182</v>
       </c>
       <c r="L52" t="n">
-        <v>7.953643939018249</v>
+        <v>7.988063886165619</v>
       </c>
     </row>
   </sheetData>
